--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_29sep26_Tue.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_29sep26_Tue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E255A153-7061-45FD-88F0-30F84FE82B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5170CBF5-D4FA-41B9-AD63-DF1D44097A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3509" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="319">
   <si>
     <t>Date</t>
   </si>
@@ -1154,7 +1154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1312,18 +1312,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1688,7 +1676,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
@@ -1723,13 +1711,13 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B2, $C$2:$C$695, C2, $D$2:$D$695, D2, $E$2:$E$695, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$695, B2, $C$2:$C$695, C2, $D$2:$D$695, D2, $E$2:$E$695, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
       <c r="P2" s="24"/>
     </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>62</v>
       </c>
@@ -1764,13 +1752,13 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B3, $C$2:$C$695, C3, $D$2:$D$695, D3, $E$2:$E$695, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
     </row>
-    <row r="4" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3">
         <v>46275.457638888889</v>
       </c>
@@ -1812,13 +1800,13 @@
         <v>34175</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B4, $C$2:$C$695, C4, $D$2:$D$695, D4, $E$2:$E$695, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
       <c r="P4" s="10"/>
     </row>
-    <row r="5" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>46252.645138888889</v>
       </c>
@@ -1853,13 +1841,13 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B5, $C$2:$C$695, C5, $D$2:$D$695, D5, $E$2:$E$695, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
     </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" customFormat="1" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
         <v>62</v>
       </c>
@@ -1892,13 +1880,13 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B6, $C$2:$C$695, C6, $D$2:$D$695, D6, $E$2:$E$695, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="25"/>
       <c r="P6" s="10"/>
     </row>
-    <row r="7" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
         <v>62</v>
       </c>
@@ -1933,13 +1921,13 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B7, $C$2:$C$695, C7, $D$2:$D$695, D7, $E$2:$E$695, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
       <c r="P7" s="25"/>
     </row>
-    <row r="8" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="3">
         <v>46261.375</v>
       </c>
@@ -1981,13 +1969,13 @@
         <v>350</v>
       </c>
       <c r="N8" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B8, $C$2:$C$695, C8, $D$2:$D$695, D8, $E$2:$E$695, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
       <c r="P8" s="10"/>
     </row>
-    <row r="9" spans="1:16" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -2020,13 +2008,13 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B9, $C$2:$C$695, C9, $D$2:$D$695, D9, $E$2:$E$695, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="19"/>
       <c r="P9" s="10"/>
     </row>
-    <row r="10" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2061,11 +2049,11 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B10, $C$2:$C$695, C10, $D$2:$D$695, D10, $E$2:$E$695, E10) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="6" t="s">
         <v>62</v>
       </c>
@@ -2100,11 +2088,11 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B11, $C$2:$C$695, C11, $D$2:$D$695, D11, $E$2:$E$695, E11) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3">
         <v>46268.385416666664</v>
       </c>
@@ -2146,13 +2134,13 @@
         <v>500</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B12, $C$2:$C$695, C12, $D$2:$D$695, D12, $E$2:$E$695, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
       <c r="P12" s="10"/>
     </row>
-    <row r="13" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="6" t="s">
         <v>62</v>
       </c>
@@ -2185,13 +2173,13 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B13, $C$2:$C$695, C13, $D$2:$D$695, D13, $E$2:$E$695, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
     </row>
-    <row r="14" spans="1:16" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
@@ -2224,13 +2212,13 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B14, $C$2:$C$695, C14, $D$2:$D$695, D14, $E$2:$E$695, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
       <c r="P14" s="10"/>
     </row>
-    <row r="15" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
         <v>62</v>
       </c>
@@ -2265,11 +2253,11 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B15, $C$2:$C$695, C15, $D$2:$D$695, D15, $E$2:$E$695, E15) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6" t="s">
         <v>62</v>
       </c>
@@ -2304,13 +2292,13 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B16, $C$2:$C$695, C16, $D$2:$D$695, D16, $E$2:$E$695, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16"/>
       <c r="P16"/>
     </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="6" t="s">
         <v>62</v>
       </c>
@@ -2345,13 +2333,13 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B17, $C$2:$C$695, C17, $D$2:$D$695, D17, $E$2:$E$695, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17"/>
       <c r="P17"/>
     </row>
-    <row r="18" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>46252.6875</v>
       </c>
@@ -2386,11 +2374,11 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B18, $C$2:$C$695, C18, $D$2:$D$695, D18, $E$2:$E$695, E18) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="40.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="40.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
@@ -2423,13 +2411,13 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B19, $C$2:$C$695, C19, $D$2:$D$695, D19, $E$2:$E$695, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="6" t="s">
         <v>62</v>
       </c>
@@ -2462,12 +2450,12 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B20, $C$2:$C$695, C20, $D$2:$D$695, D20, $E$2:$E$695, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
     </row>
-    <row r="21" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="3">
         <v>46283.375</v>
       </c>
@@ -2509,13 +2497,13 @@
         <v>516</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B21, $C$2:$C$695, C21, $D$2:$D$695, D21, $E$2:$E$695, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
       <c r="P21" s="10"/>
     </row>
-    <row r="22" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="3">
         <v>46261.375</v>
       </c>
@@ -2557,12 +2545,12 @@
         <v>300</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B22, $C$2:$C$695, C22, $D$2:$D$695, D22, $E$2:$E$695, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P22" s="24"/>
     </row>
-    <row r="23" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A23" s="3">
         <v>46252.6875</v>
       </c>
@@ -2597,13 +2585,13 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B23, $C$2:$C$695, C23, $D$2:$D$695, D23, $E$2:$E$695, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
       <c r="P23"/>
     </row>
-    <row r="24" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="6" t="s">
         <v>62</v>
       </c>
@@ -2638,13 +2626,13 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B24, $C$2:$C$695, C24, $D$2:$D$695, D24, $E$2:$E$695, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
         <v>62</v>
       </c>
@@ -2679,12 +2667,12 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B25, $C$2:$C$695, C25, $D$2:$D$695, D25, $E$2:$E$695, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
     </row>
-    <row r="26" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="6" t="s">
         <v>62</v>
       </c>
@@ -2719,13 +2707,13 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B26, $C$2:$C$695, C26, $D$2:$D$695, D26, $E$2:$E$695, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
       <c r="P26"/>
     </row>
-    <row r="27" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="3">
         <v>46260.375</v>
       </c>
@@ -2767,11 +2755,11 @@
         <v>300</v>
       </c>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B27, $C$2:$C$695, C27, $D$2:$D$695, D27, $E$2:$E$695, E27) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="6" t="s">
         <v>62</v>
       </c>
@@ -2804,12 +2792,12 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B28, $C$2:$C$695, C28, $D$2:$D$695, D28, $E$2:$E$695, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
     </row>
-    <row r="29" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
         <v>46287.375</v>
       </c>
@@ -2851,11 +2839,11 @@
         <v>554</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B29, $C$2:$C$695, C29, $D$2:$D$695, D29, $E$2:$E$695, E29) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="6" t="s">
         <v>62</v>
       </c>
@@ -2890,13 +2878,13 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B30, $C$2:$C$695, C30, $D$2:$D$695, D30, $E$2:$E$695, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
       <c r="P30"/>
     </row>
-    <row r="31" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
         <v>46286.375</v>
       </c>
@@ -2939,11 +2927,11 @@
         <v>225</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B31, $C$2:$C$695, C31, $D$2:$D$695, D31, $E$2:$E$695, E31) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -2978,12 +2966,12 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B32, $C$2:$C$695, C32, $D$2:$D$695, D32, $E$2:$E$695, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P32"/>
     </row>
-    <row r="33" spans="1:16" s="25" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:16" s="25" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="49">
         <v>46293.375</v>
       </c>
@@ -3025,13 +3013,13 @@
         <v>646</v>
       </c>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B33, $C$2:$C$695, C33, $D$2:$D$695, D33, $E$2:$E$695, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="10"/>
       <c r="P33" s="10"/>
     </row>
-    <row r="34" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -3066,13 +3054,13 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B34, $C$2:$C$695, C34, $D$2:$D$695, D34, $E$2:$E$695, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="6" t="s">
         <v>62</v>
       </c>
@@ -3107,11 +3095,11 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B35, $C$2:$C$695, C35, $D$2:$D$695, D35, $E$2:$E$695, E35) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="24" customFormat="1" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="24" customFormat="1" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>62</v>
       </c>
@@ -3144,13 +3132,13 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B36, $C$2:$C$695, C36, $D$2:$D$695, D36, $E$2:$E$695, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
       <c r="P36"/>
     </row>
-    <row r="37" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="6" t="s">
         <v>62</v>
       </c>
@@ -3183,13 +3171,13 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B37, $C$2:$C$695, C37, $D$2:$D$695, D37, $E$2:$E$695, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
       <c r="P37"/>
     </row>
-    <row r="38" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
@@ -3224,13 +3212,13 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B38, $C$2:$C$695, C38, $D$2:$D$695, D38, $E$2:$E$695, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
       <c r="P38"/>
     </row>
-    <row r="39" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="6" t="s">
         <v>62</v>
       </c>
@@ -3263,13 +3251,13 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B39, $C$2:$C$695, C39, $D$2:$D$695, D39, $E$2:$E$695, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" spans="1:16" ht="27.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:16" ht="27.65" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="3">
         <v>46286.527083333334</v>
       </c>
@@ -3311,11 +3299,11 @@
         <v>314</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B40, $C$2:$C$695, C40, $D$2:$D$695, D40, $E$2:$E$695, E40) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="3">
         <v>46258.601388888892</v>
       </c>
@@ -3357,13 +3345,13 @@
         <v>300</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B41, $C$2:$C$695, C41, $D$2:$D$695, D41, $E$2:$E$695, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
       <c r="P41"/>
     </row>
-    <row r="42" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A42" s="6" t="s">
         <v>62</v>
       </c>
@@ -3396,13 +3384,13 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B42, $C$2:$C$695, C42, $D$2:$D$695, D42, $E$2:$E$695, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
       <c r="P42"/>
     </row>
-    <row r="43" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="6" t="s">
         <v>62</v>
       </c>
@@ -3435,13 +3423,13 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B43, $C$2:$C$695, C43, $D$2:$D$695, D43, $E$2:$E$695, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
       <c r="P43"/>
     </row>
-    <row r="44" spans="1:16" s="24" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:16" s="24" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A44" s="6" t="s">
         <v>62</v>
       </c>
@@ -3474,13 +3462,13 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B44, $C$2:$C$695, C44, $D$2:$D$695, D44, $E$2:$E$695, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
       <c r="P44"/>
     </row>
-    <row r="45" spans="1:16" s="29" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:16" s="29" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="6" t="s">
         <v>62</v>
       </c>
@@ -3515,13 +3503,13 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B45, $C$2:$C$695, C45, $D$2:$D$695, D45, $E$2:$E$695, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="6" t="s">
         <v>62</v>
       </c>
@@ -3554,13 +3542,13 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B46, $C$2:$C$695, C46, $D$2:$D$695, D46, $E$2:$E$695, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
       <c r="P46"/>
     </row>
-    <row r="47" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="6" t="s">
         <v>62</v>
       </c>
@@ -3593,13 +3581,13 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B47, $C$2:$C$695, C47, $D$2:$D$695, D47, $E$2:$E$695, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
       <c r="P47"/>
     </row>
-    <row r="48" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="3">
         <v>46254.375</v>
       </c>
@@ -3627,7 +3615,7 @@
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="58" t="s">
+      <c r="J48" s="17" t="s">
         <v>55</v>
       </c>
       <c r="K48" s="17" t="s">
@@ -3636,11 +3624,11 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B48, $C$2:$C$695, C48, $D$2:$D$695, D48, $E$2:$E$695, E48) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="3">
         <v>46121.375</v>
       </c>
@@ -3668,7 +3656,7 @@
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="56" t="s">
+      <c r="J49" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K49" s="18" t="s">
@@ -3683,11 +3671,11 @@
         <v>540</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B49, $C$2:$C$695, C49, $D$2:$D$695, D49, $E$2:$E$695, E49) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="49">
         <v>46289.375</v>
       </c>
@@ -3715,7 +3703,7 @@
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="56" t="s">
+      <c r="J50" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K50" s="18" t="s">
@@ -3729,13 +3717,13 @@
         <v>240</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B50, $C$2:$C$695, C50, $D$2:$D$695, D50, $E$2:$E$695, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="10"/>
       <c r="P50" s="10"/>
     </row>
-    <row r="51" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="3">
         <v>46031.4375</v>
       </c>
@@ -3763,7 +3751,7 @@
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="56" t="s">
+      <c r="J51" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K51" s="18"/>
@@ -3773,7 +3761,7 @@
         <v>3156</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B51, $C$2:$C$695, C51, $D$2:$D$695, D51, $E$2:$E$695, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="10"/>
@@ -3821,13 +3809,13 @@
         <v>500</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B52, $C$2:$C$695, C52, $D$2:$D$695, D52, $E$2:$E$695, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
       <c r="P52" s="10"/>
     </row>
-    <row r="53" spans="1:16" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:16" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="6" t="s">
         <v>62</v>
       </c>
@@ -3855,16 +3843,16 @@
       <c r="I53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J53" s="55"/>
+      <c r="J53" s="51"/>
       <c r="K53" s="17"/>
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B53, $C$2:$C$695, C53, $D$2:$D$695, D53, $E$2:$E$695, E53) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="6" t="s">
         <v>62</v>
       </c>
@@ -3892,18 +3880,18 @@
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="55"/>
+      <c r="J54" s="51"/>
       <c r="K54" s="17"/>
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B54, $C$2:$C$695, C54, $D$2:$D$695, D54, $E$2:$E$695, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
       <c r="P54"/>
     </row>
-    <row r="55" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="6" t="s">
         <v>62</v>
       </c>
@@ -3931,18 +3919,18 @@
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="55"/>
+      <c r="J55" s="51"/>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B55, $C$2:$C$695, C55, $D$2:$D$695, D55, $E$2:$E$695, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
       <c r="P55"/>
     </row>
-    <row r="56" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="3">
         <v>46288.479861111111</v>
       </c>
@@ -3970,7 +3958,7 @@
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="56" t="s">
+      <c r="J56" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K56" s="18" t="s">
@@ -3984,13 +3972,13 @@
         <v>250</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B56, $C$2:$C$695, C56, $D$2:$D$695, D56, $E$2:$E$695, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="10"/>
       <c r="P56" s="10"/>
     </row>
-    <row r="57" spans="1:16" s="25" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:16" s="25" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="3">
         <v>46252.635416666664</v>
       </c>
@@ -4018,18 +4006,18 @@
       <c r="I57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="55"/>
+      <c r="J57" s="51"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B57, $C$2:$C$695, C57, $D$2:$D$695, D57, $E$2:$E$695, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="6" t="s">
         <v>62</v>
       </c>
@@ -4057,18 +4045,18 @@
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="55"/>
+      <c r="J58" s="51"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B58, $C$2:$C$695, C58, $D$2:$D$695, D58, $E$2:$E$695, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
       <c r="P58"/>
     </row>
-    <row r="59" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="6" t="s">
         <v>62</v>
       </c>
@@ -4096,20 +4084,20 @@
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="55" t="s">
+      <c r="J59" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B59, $C$2:$C$695, C59, $D$2:$D$695, D59, $E$2:$E$695, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
@@ -4137,14 +4125,14 @@
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="55" t="s">
+      <c r="J60" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K60" s="17"/>
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B60, $C$2:$C$695, C60, $D$2:$D$695, D60, $E$2:$E$695, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -4192,14 +4180,14 @@
         <v>1200</v>
       </c>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B61, $C$2:$C$695, C61, $D$2:$D$695, D61, $E$2:$E$695, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="38" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="6" t="s">
         <v>62</v>
       </c>
@@ -4227,20 +4215,20 @@
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="57" t="s">
+      <c r="J62" s="52" t="s">
         <v>41</v>
       </c>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B62, $C$2:$C$695, C62, $D$2:$D$695, D62, $E$2:$E$695, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
       <c r="P62"/>
     </row>
-    <row r="63" spans="1:16" s="29" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:16" s="29" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="3">
         <v>46281.416666666664</v>
       </c>
@@ -4268,7 +4256,7 @@
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="56" t="s">
+      <c r="J63" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K63" s="18" t="s">
@@ -4282,13 +4270,13 @@
         <v>10680</v>
       </c>
       <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B63, $C$2:$C$695, C63, $D$2:$D$695, D63, $E$2:$E$695, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63" s="10"/>
       <c r="P63" s="10"/>
     </row>
-    <row r="64" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="6" t="s">
         <v>62</v>
       </c>
@@ -4316,14 +4304,14 @@
       <c r="I64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J64" s="55" t="s">
+      <c r="J64" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K64" s="17"/>
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B64, $C$2:$C$695, C64, $D$2:$D$695, D64, $E$2:$E$695, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -4371,11 +4359,11 @@
         <v>650</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B65, $C$2:$C$695, C65, $D$2:$D$695, D65, $E$2:$E$695, E65) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" s="24" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" s="24" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A66" s="3">
         <v>46252.688194444447</v>
       </c>
@@ -4403,20 +4391,20 @@
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="55" t="s">
+      <c r="J66" s="51" t="s">
         <v>55</v>
       </c>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B66, $C$2:$C$695, C66, $D$2:$D$695, D66, $E$2:$E$695, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$695, B66, $C$2:$C$695, C66, $D$2:$D$695, D66, $E$2:$E$695, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
       <c r="P66"/>
     </row>
-    <row r="67" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A67" s="3">
         <v>46281.416666666664</v>
       </c>
@@ -4444,7 +4432,7 @@
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="56" t="s">
+      <c r="J67" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K67" s="18" t="s">
@@ -4458,7 +4446,7 @@
         <v>10880</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B67, $C$2:$C$695, C67, $D$2:$D$695, D67, $E$2:$E$695, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4504,7 +4492,7 @@
         <v>1000</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B68, $C$2:$C$695, C68, $D$2:$D$695, D68, $E$2:$E$695, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4550,7 +4538,7 @@
         <v>288</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B69, $C$2:$C$695, C69, $D$2:$D$695, D69, $E$2:$E$695, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4596,7 +4584,7 @@
         <v>360</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B70, $C$2:$C$695, C70, $D$2:$D$695, D70, $E$2:$E$695, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70" s="38" t="s">
@@ -4645,13 +4633,13 @@
         <v>300</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B71, $C$2:$C$695, C71, $D$2:$D$695, D71, $E$2:$E$695, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="10"/>
       <c r="P71" s="10"/>
     </row>
-    <row r="72" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="6" t="s">
         <v>62</v>
       </c>
@@ -4679,14 +4667,14 @@
       <c r="I72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="55" t="s">
+      <c r="J72" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K72" s="17"/>
       <c r="L72" s="17"/>
       <c r="M72" s="17"/>
       <c r="N72" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B72, $C$2:$C$695, C72, $D$2:$D$695, D72, $E$2:$E$695, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72"/>
@@ -4730,11 +4718,11 @@
         <v>16755</v>
       </c>
       <c r="M73" s="18">
-        <f>ABS((D73*E73)-L73)</f>
+        <f t="shared" ref="M73:M79" si="2">ABS((D73*E73)-L73)</f>
         <v>295</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B73, $C$2:$C$695, C73, $D$2:$D$695, D73, $E$2:$E$695, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4777,11 +4765,11 @@
         <v>3160</v>
       </c>
       <c r="M74" s="18">
-        <f>ABS((D74*E74)-L74)</f>
+        <f t="shared" si="2"/>
         <v>235</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B74, $C$2:$C$695, C74, $D$2:$D$695, D74, $E$2:$E$695, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4823,11 +4811,11 @@
         <v>4640</v>
       </c>
       <c r="M75" s="18">
-        <f>ABS((D75*E75)-L75)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B75, $C$2:$C$695, C75, $D$2:$D$695, D75, $E$2:$E$695, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="38" t="s">
@@ -4872,11 +4860,11 @@
         <v>33200</v>
       </c>
       <c r="M76" s="18">
-        <f>ABS((D76*E76)-L76)</f>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B76, $C$2:$C$695, C76, $D$2:$D$695, D76, $E$2:$E$695, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4918,11 +4906,11 @@
         <v>19550</v>
       </c>
       <c r="M77" s="18">
-        <f>ABS((D77*E77)-L77)</f>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B77, $C$2:$C$695, C77, $D$2:$D$695, D77, $E$2:$E$695, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4964,11 +4952,11 @@
         <v>8420</v>
       </c>
       <c r="M78" s="18">
-        <f>ABS((D78*E78)-L78)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B78, $C$2:$C$695, C78, $D$2:$D$695, D78, $E$2:$E$695, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="10"/>
@@ -5012,11 +5000,11 @@
         <v>6367.2</v>
       </c>
       <c r="M79" s="18">
-        <f>ABS((D79*E79)-L79)</f>
+        <f t="shared" si="2"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B79, $C$2:$C$695, C79, $D$2:$D$695, D79, $E$2:$E$695, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="38" t="s">
@@ -5024,7 +5012,7 @@
       </c>
       <c r="P79" s="10"/>
     </row>
-    <row r="80" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="6" t="s">
         <v>62</v>
       </c>
@@ -5052,12 +5040,12 @@
       <c r="I80" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="55"/>
+      <c r="J80" s="51"/>
       <c r="K80" s="17"/>
       <c r="L80" s="17"/>
       <c r="M80" s="17"/>
       <c r="N80" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B80, $C$2:$C$695, C80, $D$2:$D$695, D80, $E$2:$E$695, E80) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O80"/>
@@ -5101,11 +5089,11 @@
         <v>8570</v>
       </c>
       <c r="M81" s="27">
-        <f>ABS((D81*E81)-L81)</f>
+        <f t="shared" ref="M81:M99" si="3">ABS((D81*E81)-L81)</f>
         <v>650</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B81, $C$2:$C$695, C81, $D$2:$D$695, D81, $E$2:$E$695, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="38" t="s">
@@ -5150,11 +5138,11 @@
         <v>39300</v>
       </c>
       <c r="M82" s="18">
-        <f>ABS((D82*E82)-L82)</f>
+        <f t="shared" si="3"/>
         <v>18850</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B82, $C$2:$C$695, C82, $D$2:$D$695, D82, $E$2:$E$695, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5196,11 +5184,11 @@
         <v>8400</v>
       </c>
       <c r="M83" s="18">
-        <f>ABS((D83*E83)-L83)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B83, $C$2:$C$695, C83, $D$2:$D$695, D83, $E$2:$E$695, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5242,11 +5230,11 @@
         <v>10250</v>
       </c>
       <c r="M84" s="18">
-        <f>ABS((D84*E84)-L84)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B84, $C$2:$C$695, C84, $D$2:$D$695, D84, $E$2:$E$695, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5288,11 +5276,11 @@
         <v>35200</v>
       </c>
       <c r="M85" s="18">
-        <f>ABS((D85*E85)-L85)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B85, $C$2:$C$695, C85, $D$2:$D$695, D85, $E$2:$E$695, E85) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5334,11 +5322,11 @@
         <v>3560</v>
       </c>
       <c r="M86" s="18">
-        <f>ABS((D86*E86)-L86)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B86, $C$2:$C$695, C86, $D$2:$D$695, D86, $E$2:$E$695, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5380,11 +5368,11 @@
         <v>33950</v>
       </c>
       <c r="M87" s="18">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" si="3"/>
         <v>850</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B87, $C$2:$C$695, C87, $D$2:$D$695, D87, $E$2:$E$695, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5426,11 +5414,11 @@
         <v>11660</v>
       </c>
       <c r="M88" s="18">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B88, $C$2:$C$695, C88, $D$2:$D$695, D88, $E$2:$E$695, E88) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O88" s="38" t="s">
@@ -5475,11 +5463,11 @@
         <v>15300</v>
       </c>
       <c r="M89" s="18">
-        <f>ABS((D89*E89)-L89)</f>
+        <f t="shared" si="3"/>
         <v>420</v>
       </c>
       <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B89, $C$2:$C$695, C89, $D$2:$D$695, D89, $E$2:$E$695, E89) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5521,11 +5509,11 @@
         <v>5450</v>
       </c>
       <c r="M90" s="18">
-        <f>ABS((D90*E90)-L90)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B90, $C$2:$C$695, C90, $D$2:$D$695, D90, $E$2:$E$695, E90) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O90" s="10"/>
@@ -5569,11 +5557,11 @@
         <v>17150</v>
       </c>
       <c r="M91" s="18">
-        <f>ABS((D91*E91)-L91)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B91, $C$2:$C$695, C91, $D$2:$D$695, D91, $E$2:$E$695, E91) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5615,11 +5603,11 @@
         <v>14130</v>
       </c>
       <c r="M92" s="18">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="3"/>
         <v>714</v>
       </c>
       <c r="N92" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B92, $C$2:$C$695, C92, $D$2:$D$695, D92, $E$2:$E$695, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5662,11 +5650,11 @@
         <v>8870</v>
       </c>
       <c r="M93" s="18">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B93, $C$2:$C$695, C93, $D$2:$D$695, D93, $E$2:$E$695, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5708,11 +5696,11 @@
         <v>19730.5</v>
       </c>
       <c r="M94" s="27">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="3"/>
         <v>504.5</v>
       </c>
       <c r="N94" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B94, $C$2:$C$695, C94, $D$2:$D$695, D94, $E$2:$E$695, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O94" s="38" t="s">
@@ -5758,11 +5746,11 @@
         <v>19690</v>
       </c>
       <c r="M95" s="27">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="3"/>
         <v>545</v>
       </c>
       <c r="N95" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B95, $C$2:$C$695, C95, $D$2:$D$695, D95, $E$2:$E$695, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O95" s="38" t="s">
@@ -5807,11 +5795,11 @@
         <v>10400</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B96, $C$2:$C$695, C96, $D$2:$D$695, D96, $E$2:$E$695, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5853,11 +5841,11 @@
         <v>17040</v>
       </c>
       <c r="M97" s="18">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="3"/>
         <v>880</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B97, $C$2:$C$695, C97, $D$2:$D$695, D97, $E$2:$E$695, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O97" s="38" t="s">
@@ -5902,11 +5890,11 @@
         <v>3300</v>
       </c>
       <c r="M98" s="18">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="3"/>
         <v>250</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B98, $C$2:$C$695, C98, $D$2:$D$695, D98, $E$2:$E$695, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5948,11 +5936,11 @@
         <v>10249</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="3"/>
         <v>4451</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B99, $C$2:$C$695, C99, $D$2:$D$695, D99, $E$2:$E$695, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="38" t="s">
@@ -5991,7 +5979,7 @@
         <v>118</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B100, $C$2:$C$695, C100, $D$2:$D$695, D100, $E$2:$E$695, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6023,7 +6011,7 @@
       <c r="I101" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="56" t="s">
+      <c r="J101" s="18" t="s">
         <v>118</v>
       </c>
       <c r="K101" s="18" t="s">
@@ -6037,7 +6025,7 @@
         <v>650</v>
       </c>
       <c r="N101" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B101, $C$2:$C$695, C101, $D$2:$D$695, D101, $E$2:$E$695, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6076,7 +6064,7 @@
         <v>145</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B102, $C$2:$C$695, C102, $D$2:$D$695, D102, $E$2:$E$695, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6118,11 +6106,11 @@
         <v>6202</v>
       </c>
       <c r="M103" s="18">
-        <f>ABS((D103*E103)-L103)</f>
+        <f t="shared" ref="M103:M111" si="4">ABS((D103*E103)-L103)</f>
         <v>496</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B103, $C$2:$C$695, C103, $D$2:$D$695, D103, $E$2:$E$695, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6164,11 +6152,11 @@
         <v>15075</v>
       </c>
       <c r="M104" s="18">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B104, $C$2:$C$695, C104, $D$2:$D$695, D104, $E$2:$E$695, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104" s="38" t="s">
@@ -6213,11 +6201,11 @@
         <v>9886</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" si="4"/>
         <v>654</v>
       </c>
       <c r="N105" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B105, $C$2:$C$695, C105, $D$2:$D$695, D105, $E$2:$E$695, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6260,11 +6248,11 @@
         <v>8870</v>
       </c>
       <c r="M106" s="18">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B106, $C$2:$C$695, C106, $D$2:$D$695, D106, $E$2:$E$695, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6306,11 +6294,11 @@
         <v>39300</v>
       </c>
       <c r="M107" s="18">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="4"/>
         <v>18350</v>
       </c>
       <c r="N107" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B107, $C$2:$C$695, C107, $D$2:$D$695, D107, $E$2:$E$695, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6352,11 +6340,11 @@
         <v>20010</v>
       </c>
       <c r="M108" s="18">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B108, $C$2:$C$695, C108, $D$2:$D$695, D108, $E$2:$E$695, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="10"/>
@@ -6400,11 +6388,11 @@
         <v>8820</v>
       </c>
       <c r="M109" s="27">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N109" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B109, $C$2:$C$695, C109, $D$2:$D$695, D109, $E$2:$E$695, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6446,11 +6434,11 @@
         <v>36946</v>
       </c>
       <c r="M110" s="27">
-        <f>ABS((D110*E110)-L110)</f>
+        <f t="shared" si="4"/>
         <v>934</v>
       </c>
       <c r="N110" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B110, $C$2:$C$695, C110, $D$2:$D$695, D110, $E$2:$E$695, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O110" s="29"/>
@@ -6494,11 +6482,11 @@
         <v>20260</v>
       </c>
       <c r="M111" s="18">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N111" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B111, $C$2:$C$695, C111, $D$2:$D$695, D111, $E$2:$E$695, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O111"/>
@@ -6534,7 +6522,7 @@
       </c>
       <c r="J112" s="34"/>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B112, $C$2:$C$695, C112, $D$2:$D$695, D112, $E$2:$E$695, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="29"/>
@@ -6581,7 +6569,7 @@
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B113, $C$2:$C$695, C113, $D$2:$D$695, D113, $E$2:$E$695, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6627,7 +6615,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B114, $C$2:$C$695, C114, $D$2:$D$695, D114, $E$2:$E$695, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P114"/>
@@ -6674,7 +6662,7 @@
         <v>1700</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B115, $C$2:$C$695, C115, $D$2:$D$695, D115, $E$2:$E$695, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="29"/>
@@ -6721,7 +6709,7 @@
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B116, $C$2:$C$695, C116, $D$2:$D$695, D116, $E$2:$E$695, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P116" s="29"/>
@@ -6756,7 +6744,7 @@
       </c>
       <c r="J117" s="34"/>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B117, $C$2:$C$695, C117, $D$2:$D$695, D117, $E$2:$E$695, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6802,7 +6790,7 @@
         <v>300</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B118, $C$2:$C$695, C118, $D$2:$D$695, D118, $E$2:$E$695, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6849,7 +6837,7 @@
         <v>300</v>
       </c>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B119, $C$2:$C$695, C119, $D$2:$D$695, D119, $E$2:$E$695, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6883,7 +6871,7 @@
       </c>
       <c r="J120" s="34"/>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B120, $C$2:$C$695, C120, $D$2:$D$695, D120, $E$2:$E$695, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="38" t="s">
@@ -6933,7 +6921,7 @@
         <v>1400</v>
       </c>
       <c r="N121" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B121, $C$2:$C$695, C121, $D$2:$D$695, D121, $E$2:$E$695, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="38" t="s">
@@ -6983,7 +6971,7 @@
         <v>270</v>
       </c>
       <c r="N122" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B122, $C$2:$C$695, C122, $D$2:$D$695, D122, $E$2:$E$695, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="39" t="s">
@@ -7033,7 +7021,7 @@
         <v>188.60000000000014</v>
       </c>
       <c r="N123" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B123, $C$2:$C$695, C123, $D$2:$D$695, D123, $E$2:$E$695, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="39" t="s">
@@ -7083,7 +7071,7 @@
         <v>280</v>
       </c>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B124, $C$2:$C$695, C124, $D$2:$D$695, D124, $E$2:$E$695, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="38" t="s">
@@ -7132,7 +7120,7 @@
         <v>376</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B125, $C$2:$C$695, C125, $D$2:$D$695, D125, $E$2:$E$695, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7171,13 +7159,13 @@
       <c r="L126" s="18"/>
       <c r="M126" s="18"/>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B126, $C$2:$C$695, C126, $D$2:$D$695, D126, $E$2:$E$695, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="10"/>
       <c r="P126" s="10"/>
     </row>
-    <row r="127" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A127" s="6" t="s">
         <v>62</v>
       </c>
@@ -7205,14 +7193,14 @@
       <c r="I127" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J127" s="55" t="s">
+      <c r="J127" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K127" s="17"/>
       <c r="L127" s="17"/>
       <c r="M127" s="17"/>
       <c r="N127" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B127, $C$2:$C$695, C127, $D$2:$D$695, D127, $E$2:$E$695, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127"/>
@@ -7260,7 +7248,7 @@
         <v>500</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B128, $C$2:$C$695, C128, $D$2:$D$695, D128, $E$2:$E$695, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7296,7 +7284,7 @@
         <v>118</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B129, $C$2:$C$695, C129, $D$2:$D$695, D129, $E$2:$E$695, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7330,7 +7318,7 @@
       </c>
       <c r="J130" s="34"/>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B130, $C$2:$C$695, C130, $D$2:$D$695, D130, $E$2:$E$695, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$695, B130, $C$2:$C$695, C130, $D$2:$D$695, D130, $E$2:$E$695, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -7376,7 +7364,7 @@
         <v>1000</v>
       </c>
       <c r="N131" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B131, $C$2:$C$695, C131, $D$2:$D$695, D131, $E$2:$E$695, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="10"/>
@@ -7414,7 +7402,7 @@
         <v>118</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B132, $C$2:$C$695, C132, $D$2:$D$695, D132, $E$2:$E$695, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P132"/>
@@ -7449,7 +7437,7 @@
       </c>
       <c r="J133" s="34"/>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B133, $C$2:$C$695, C133, $D$2:$D$695, D133, $E$2:$E$695, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7495,7 +7483,7 @@
         <v>290</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B134, $C$2:$C$695, C134, $D$2:$D$695, D134, $E$2:$E$695, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="10"/>
@@ -7533,7 +7521,7 @@
         <v>117</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B135, $C$2:$C$695, C135, $D$2:$D$695, D135, $E$2:$E$695, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7575,11 +7563,11 @@
         <v>10410</v>
       </c>
       <c r="M136" s="18">
-        <f>ABS((D136*E136)-L136)</f>
+        <f t="shared" ref="M136:M142" si="6">ABS((D136*E136)-L136)</f>
         <v>300</v>
       </c>
       <c r="N136" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B136, $C$2:$C$695, C136, $D$2:$D$695, D136, $E$2:$E$695, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="29"/>
@@ -7622,11 +7610,11 @@
         <v>14552</v>
       </c>
       <c r="M137" s="18">
-        <f>ABS((D137*E137)-L137)</f>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B137, $C$2:$C$695, C137, $D$2:$D$695, D137, $E$2:$E$695, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="38" t="s">
@@ -7672,11 +7660,11 @@
         <v>3400</v>
       </c>
       <c r="M138" s="18">
-        <f>ABS((D138*E138)-L138)</f>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B138, $C$2:$C$695, C138, $D$2:$D$695, D138, $E$2:$E$695, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7718,11 +7706,11 @@
         <v>5370</v>
       </c>
       <c r="M139" s="27">
-        <f>ABS((D139*E139)-L139)</f>
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
       <c r="N139" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B139, $C$2:$C$695, C139, $D$2:$D$695, D139, $E$2:$E$695, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7764,11 +7752,11 @@
         <v>2610</v>
       </c>
       <c r="M140" s="27">
-        <f>ABS((D140*E140)-L140)</f>
+        <f t="shared" si="6"/>
         <v>235</v>
       </c>
       <c r="N140" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B140, $C$2:$C$695, C140, $D$2:$D$695, D140, $E$2:$E$695, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7810,11 +7798,11 @@
         <v>9170</v>
       </c>
       <c r="M141" s="27">
-        <f>ABS((D141*E141)-L141)</f>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B141, $C$2:$C$695, C141, $D$2:$D$695, D141, $E$2:$E$695, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O141" s="38" t="s">
@@ -7859,11 +7847,11 @@
         <v>14200</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B142, $C$2:$C$695, C142, $D$2:$D$695, D142, $E$2:$E$695, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7897,7 +7885,7 @@
       </c>
       <c r="J143" s="34"/>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B143, $C$2:$C$695, C143, $D$2:$D$695, D143, $E$2:$E$695, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="24"/>
@@ -7932,7 +7920,7 @@
       </c>
       <c r="J144" s="34"/>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B144, $C$2:$C$695, C144, $D$2:$D$695, D144, $E$2:$E$695, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7966,7 +7954,7 @@
       </c>
       <c r="J145" s="34"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B145, $C$2:$C$695, C145, $D$2:$D$695, D145, $E$2:$E$695, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8008,11 +7996,11 @@
         <v>5520</v>
       </c>
       <c r="M146" s="27">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" ref="M146:M152" si="7">ABS((D146*E146)-L146)</f>
         <v>300</v>
       </c>
       <c r="N146" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B146, $C$2:$C$695, C146, $D$2:$D$695, D146, $E$2:$E$695, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O146" s="38" t="s">
@@ -8057,11 +8045,11 @@
         <v>2657</v>
       </c>
       <c r="M147" s="27">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="N147" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B147, $C$2:$C$695, C147, $D$2:$D$695, D147, $E$2:$E$695, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O147" s="38" t="s">
@@ -8106,11 +8094,11 @@
         <v>2554.5</v>
       </c>
       <c r="M148" s="27">
-        <f>ABS((D148*E148)-L148)</f>
+        <f t="shared" si="7"/>
         <v>355.5</v>
       </c>
       <c r="N148" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B148, $C$2:$C$695, C148, $D$2:$D$695, D148, $E$2:$E$695, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O148" s="38" t="s">
@@ -8156,11 +8144,11 @@
         <v>5585</v>
       </c>
       <c r="M149" s="27">
-        <f>ABS((D149*E149)-L149)</f>
+        <f t="shared" si="7"/>
         <v>395</v>
       </c>
       <c r="N149" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B149, $C$2:$C$695, C149, $D$2:$D$695, D149, $E$2:$E$695, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O149" s="38" t="s">
@@ -8206,11 +8194,11 @@
         <v>5730</v>
       </c>
       <c r="M150" s="27">
-        <f>ABS((D150*E150)-L150)</f>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N150" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B150, $C$2:$C$695, C150, $D$2:$D$695, D150, $E$2:$E$695, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O150" s="38" t="s">
@@ -8255,11 +8243,11 @@
         <v>5940</v>
       </c>
       <c r="M151" s="18">
-        <f>ABS((D151*E151)-L151)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B151, $C$2:$C$695, C151, $D$2:$D$695, D151, $E$2:$E$695, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O151" s="10"/>
@@ -8303,11 +8291,11 @@
         <v>16580</v>
       </c>
       <c r="M152" s="44">
-        <f>ABS((D152*E152)-L152)</f>
+        <f t="shared" si="7"/>
         <v>660</v>
       </c>
       <c r="N152" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B152, $C$2:$C$695, C152, $D$2:$D$695, D152, $E$2:$E$695, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O152" s="24"/>
@@ -8347,11 +8335,11 @@
         <v>118</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B153, $C$2:$C$695, C153, $D$2:$D$695, D153, $E$2:$E$695, E153) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A154" s="6" t="s">
         <v>62</v>
       </c>
@@ -8379,14 +8367,14 @@
       <c r="I154" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J154" s="55" t="s">
+      <c r="J154" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K154" s="17"/>
       <c r="L154" s="17"/>
       <c r="M154" s="17"/>
       <c r="N154" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B154, $C$2:$C$695, C154, $D$2:$D$695, D154, $E$2:$E$695, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O154"/>
@@ -8434,7 +8422,7 @@
         <v>300</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B155, $C$2:$C$695, C155, $D$2:$D$695, D155, $E$2:$E$695, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8480,7 +8468,7 @@
         <v>940</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B156, $C$2:$C$695, C156, $D$2:$D$695, D156, $E$2:$E$695, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8516,7 +8504,7 @@
         <v>118</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B157, $C$2:$C$695, C157, $D$2:$D$695, D157, $E$2:$E$695, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8562,7 +8550,7 @@
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B158, $C$2:$C$695, C158, $D$2:$D$695, D158, $E$2:$E$695, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8608,7 +8596,7 @@
         <v>275</v>
       </c>
       <c r="N159" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B159, $C$2:$C$695, C159, $D$2:$D$695, D159, $E$2:$E$695, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8654,7 +8642,7 @@
         <v>225</v>
       </c>
       <c r="N160" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B160, $C$2:$C$695, C160, $D$2:$D$695, D160, $E$2:$E$695, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8700,12 +8688,12 @@
         <v>300</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B161, $C$2:$C$695, C161, $D$2:$D$695, D161, $E$2:$E$695, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O161"/>
     </row>
-    <row r="162" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A162" s="30">
         <v>46258.443749999999</v>
       </c>
@@ -8747,11 +8735,11 @@
         <v>527.5</v>
       </c>
       <c r="N162" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B162, $C$2:$C$695, C162, $D$2:$D$695, D162, $E$2:$E$695, E162) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A163" s="40">
         <v>46253.4</v>
       </c>
@@ -8788,7 +8776,7 @@
       <c r="L163" s="27"/>
       <c r="M163" s="27"/>
       <c r="N163" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B163, $C$2:$C$695, C163, $D$2:$D$695, D163, $E$2:$E$695, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O163" s="29"/>
@@ -8836,7 +8824,7 @@
         <v>500</v>
       </c>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B164, $C$2:$C$695, C164, $D$2:$D$695, D164, $E$2:$E$695, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8872,7 +8860,7 @@
         <v>118</v>
       </c>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B165, $C$2:$C$695, C165, $D$2:$D$695, D165, $E$2:$E$695, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8918,7 +8906,7 @@
         <v>800</v>
       </c>
       <c r="N166" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B166, $C$2:$C$695, C166, $D$2:$D$695, D166, $E$2:$E$695, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8955,7 +8943,7 @@
       <c r="L167" s="18"/>
       <c r="M167" s="18"/>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B167, $C$2:$C$695, C167, $D$2:$D$695, D167, $E$2:$E$695, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O167" s="10"/>
@@ -8991,7 +8979,7 @@
       </c>
       <c r="J168" s="34"/>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B168, $C$2:$C$695, C168, $D$2:$D$695, D168, $E$2:$E$695, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P168" s="29"/>
@@ -9038,7 +9026,7 @@
         <v>810</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B169, $C$2:$C$695, C169, $D$2:$D$695, D169, $E$2:$E$695, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9084,7 +9072,7 @@
         <v>300</v>
       </c>
       <c r="N170" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B170, $C$2:$C$695, C170, $D$2:$D$695, D170, $E$2:$E$695, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9130,7 +9118,7 @@
         <v>300</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B171, $C$2:$C$695, C171, $D$2:$D$695, D171, $E$2:$E$695, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P171" s="19"/>
@@ -9177,7 +9165,7 @@
         <v>501</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B172, $C$2:$C$695, C172, $D$2:$D$695, D172, $E$2:$E$695, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="38" t="s">
@@ -9226,7 +9214,7 @@
         <v>650</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B173, $C$2:$C$695, C173, $D$2:$D$695, D173, $E$2:$E$695, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="29"/>
@@ -9263,7 +9251,7 @@
         <v>195</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B174, $C$2:$C$695, C174, $D$2:$D$695, D174, $E$2:$E$695, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9309,7 +9297,7 @@
         <v>450</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B175, $C$2:$C$695, C175, $D$2:$D$695, D175, $E$2:$E$695, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9355,7 +9343,7 @@
         <v>300</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B176, $C$2:$C$695, C176, $D$2:$D$695, D176, $E$2:$E$695, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9391,7 +9379,7 @@
         <v>117</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B177, $C$2:$C$695, C177, $D$2:$D$695, D177, $E$2:$E$695, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9437,7 +9425,7 @@
         <v>646</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B178, $C$2:$C$695, C178, $D$2:$D$695, D178, $E$2:$E$695, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O178" s="38" t="s">
@@ -9474,7 +9462,7 @@
       </c>
       <c r="J179" s="34"/>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B179, $C$2:$C$695, C179, $D$2:$D$695, D179, $E$2:$E$695, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9510,7 +9498,7 @@
         <v>118</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B180, $C$2:$C$695, C180, $D$2:$D$695, D180, $E$2:$E$695, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="29"/>
@@ -9545,7 +9533,7 @@
       </c>
       <c r="J181" s="34"/>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B181, $C$2:$C$695, C181, $D$2:$D$695, D181, $E$2:$E$695, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9591,7 +9579,7 @@
         <v>500</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B182, $C$2:$C$695, C182, $D$2:$D$695, D182, $E$2:$E$695, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O182" s="39" t="s">
@@ -9630,7 +9618,7 @@
         <v>118</v>
       </c>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B183, $C$2:$C$695, C183, $D$2:$D$695, D183, $E$2:$E$695, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="38" t="s">
@@ -9679,7 +9667,7 @@
         <v>650</v>
       </c>
       <c r="N184" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B184, $C$2:$C$695, C184, $D$2:$D$695, D184, $E$2:$E$695, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P184" s="29"/>
@@ -9726,11 +9714,11 @@
         <v>300</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B185, $C$2:$C$695, C185, $D$2:$D$695, D185, $E$2:$E$695, E185) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="186" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="5"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A186" s="8" t="s">
         <v>62</v>
       </c>
@@ -9765,7 +9753,7 @@
       <c r="L186" s="18"/>
       <c r="M186" s="18"/>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B186, $C$2:$C$695, C186, $D$2:$D$695, D186, $E$2:$E$695, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="10"/>
@@ -9809,11 +9797,11 @@
         <v>8049</v>
       </c>
       <c r="M187" s="18">
-        <f>ABS((D187*E187)-L187)</f>
+        <f t="shared" ref="M187:M192" si="8">ABS((D187*E187)-L187)</f>
         <v>800</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B187, $C$2:$C$695, C187, $D$2:$D$695, D187, $E$2:$E$695, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O187" s="38" t="s">
@@ -9858,11 +9846,11 @@
         <v>4680</v>
       </c>
       <c r="M188" s="27">
-        <f>ABS((D188*E188)-L188)</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="N188" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B188, $C$2:$C$695, C188, $D$2:$D$695, D188, $E$2:$E$695, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="P188" s="29"/>
@@ -9905,11 +9893,11 @@
         <v>4520</v>
       </c>
       <c r="M189" s="27">
-        <f>ABS((D189*E189)-L189)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N189" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B189, $C$2:$C$695, C189, $D$2:$D$695, D189, $E$2:$E$695, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9951,11 +9939,11 @@
         <v>5905</v>
       </c>
       <c r="M190" s="18">
-        <f>ABS((D190*E190)-L190)</f>
+        <f t="shared" si="8"/>
         <v>275</v>
       </c>
       <c r="N190" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B190, $C$2:$C$695, C190, $D$2:$D$695, D190, $E$2:$E$695, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9997,11 +9985,11 @@
         <v>11175</v>
       </c>
       <c r="M191" s="27">
-        <f>ABS((D191*E191)-L191)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N191" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B191, $C$2:$C$695, C191, $D$2:$D$695, D191, $E$2:$E$695, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="29"/>
@@ -10045,11 +10033,11 @@
         <v>4402</v>
       </c>
       <c r="M192" s="27">
-        <f>ABS((D192*E192)-L192)</f>
+        <f t="shared" si="8"/>
         <v>188</v>
       </c>
       <c r="N192" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B192, $C$2:$C$695, C192, $D$2:$D$695, D192, $E$2:$E$695, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="29"/>
@@ -10090,7 +10078,7 @@
       <c r="L193" s="44"/>
       <c r="M193" s="44"/>
       <c r="N193" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B193, $C$2:$C$695, C193, $D$2:$D$695, D193, $E$2:$E$695, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O193" s="24"/>
@@ -10128,7 +10116,7 @@
       </c>
       <c r="J194" s="34"/>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B194, $C$2:$C$695, C194, $D$2:$D$695, D194, $E$2:$E$695, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$695, B194, $C$2:$C$695, C194, $D$2:$D$695, D194, $E$2:$E$695, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10174,7 +10162,7 @@
         <v>48320</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B195, $C$2:$C$695, C195, $D$2:$D$695, D195, $E$2:$E$695, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="38" t="s">
@@ -10224,7 +10212,7 @@
         <v>300</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B196, $C$2:$C$695, C196, $D$2:$D$695, D196, $E$2:$E$695, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P196" s="25"/>
@@ -10261,7 +10249,7 @@
         <v>118</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B197, $C$2:$C$695, C197, $D$2:$D$695, D197, $E$2:$E$695, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O197" s="29"/>
@@ -10308,7 +10296,7 @@
         <v>300</v>
       </c>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B198, $C$2:$C$695, C198, $D$2:$D$695, D198, $E$2:$E$695, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10354,7 +10342,7 @@
         <v>250</v>
       </c>
       <c r="N199" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B199, $C$2:$C$695, C199, $D$2:$D$695, D199, $E$2:$E$695, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10400,7 +10388,7 @@
         <v>294</v>
       </c>
       <c r="N200" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B200, $C$2:$C$695, C200, $D$2:$D$695, D200, $E$2:$E$695, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10446,7 +10434,7 @@
         <v>294</v>
       </c>
       <c r="N201" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B201, $C$2:$C$695, C201, $D$2:$D$695, D201, $E$2:$E$695, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10492,7 +10480,7 @@
         <v>280</v>
       </c>
       <c r="N202" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B202, $C$2:$C$695, C202, $D$2:$D$695, D202, $E$2:$E$695, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="29"/>
@@ -10530,7 +10518,7 @@
         <v>55</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B203, $C$2:$C$695, C203, $D$2:$D$695, D203, $E$2:$E$695, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10576,7 +10564,7 @@
         <v>650</v>
       </c>
       <c r="N204" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B204, $C$2:$C$695, C204, $D$2:$D$695, D204, $E$2:$E$695, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P204" s="29"/>
@@ -10611,7 +10599,7 @@
       </c>
       <c r="J205" s="34"/>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B205, $C$2:$C$695, C205, $D$2:$D$695, D205, $E$2:$E$695, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10657,7 +10645,7 @@
         <v>150</v>
       </c>
       <c r="N206" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B206, $C$2:$C$695, C206, $D$2:$D$695, D206, $E$2:$E$695, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10703,7 +10691,7 @@
         <v>250</v>
       </c>
       <c r="N207" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B207, $C$2:$C$695, C207, $D$2:$D$695, D207, $E$2:$E$695, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10739,7 +10727,7 @@
         <v>117</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B208, $C$2:$C$695, C208, $D$2:$D$695, D208, $E$2:$E$695, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10773,7 +10761,7 @@
       </c>
       <c r="J209" s="34"/>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B209, $C$2:$C$695, C209, $D$2:$D$695, D209, $E$2:$E$695, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10819,7 +10807,7 @@
         <v>450</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B210, $C$2:$C$695, C210, $D$2:$D$695, D210, $E$2:$E$695, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10865,7 +10853,7 @@
         <v>290</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B211, $C$2:$C$695, C211, $D$2:$D$695, D211, $E$2:$E$695, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10901,7 +10889,7 @@
         <v>118</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B212, $C$2:$C$695, C212, $D$2:$D$695, D212, $E$2:$E$695, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O212" s="29"/>
@@ -10948,7 +10936,7 @@
         <v>250</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B213, $C$2:$C$695, C213, $D$2:$D$695, D213, $E$2:$E$695, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P213" s="29"/>
@@ -10995,7 +10983,7 @@
         <v>250</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B214, $C$2:$C$695, C214, $D$2:$D$695, D214, $E$2:$E$695, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11041,7 +11029,7 @@
         <v>300</v>
       </c>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B215, $C$2:$C$695, C215, $D$2:$D$695, D215, $E$2:$E$695, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11087,7 +11075,7 @@
         <v>47900</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B216, $C$2:$C$695, C216, $D$2:$D$695, D216, $E$2:$E$695, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="38" t="s">
@@ -11124,7 +11112,7 @@
       </c>
       <c r="J217" s="34"/>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B217, $C$2:$C$695, C217, $D$2:$D$695, D217, $E$2:$E$695, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11170,7 +11158,7 @@
         <v>816</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B218, $C$2:$C$695, C218, $D$2:$D$695, D218, $E$2:$E$695, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11216,7 +11204,7 @@
         <v>650</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B219, $C$2:$C$695, C219, $D$2:$D$695, D219, $E$2:$E$695, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O219" s="38" t="s">
@@ -11265,7 +11253,7 @@
         <v>495</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B220, $C$2:$C$695, C220, $D$2:$D$695, D220, $E$2:$E$695, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O220" s="38" t="s">
@@ -11302,7 +11290,7 @@
       </c>
       <c r="J221" s="34"/>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B221, $C$2:$C$695, C221, $D$2:$D$695, D221, $E$2:$E$695, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11336,7 +11324,7 @@
       </c>
       <c r="J222" s="34"/>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B222, $C$2:$C$695, C222, $D$2:$D$695, D222, $E$2:$E$695, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11372,7 +11360,7 @@
         <v>118</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B223, $C$2:$C$695, C223, $D$2:$D$695, D223, $E$2:$E$695, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11418,7 +11406,7 @@
         <v>480</v>
       </c>
       <c r="N224" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B224, $C$2:$C$695, C224, $D$2:$D$695, D224, $E$2:$E$695, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11454,7 +11442,7 @@
         <v>55</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B225, $C$2:$C$695, C225, $D$2:$D$695, D225, $E$2:$E$695, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11490,7 +11478,7 @@
         <v>117</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B226, $C$2:$C$695, C226, $D$2:$D$695, D226, $E$2:$E$695, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11536,7 +11524,7 @@
         <v>268</v>
       </c>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B227, $C$2:$C$695, C227, $D$2:$D$695, D227, $E$2:$E$695, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11582,7 +11570,7 @@
         <v>320</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B228, $C$2:$C$695, C228, $D$2:$D$695, D228, $E$2:$E$695, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11628,7 +11616,7 @@
         <v>448</v>
       </c>
       <c r="N229" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B229, $C$2:$C$695, C229, $D$2:$D$695, D229, $E$2:$E$695, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11664,7 +11652,7 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B230, $C$2:$C$695, C230, $D$2:$D$695, D230, $E$2:$E$695, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11710,7 +11698,7 @@
         <v>300</v>
       </c>
       <c r="N231" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B231, $C$2:$C$695, C231, $D$2:$D$695, D231, $E$2:$E$695, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="38" t="s">
@@ -11748,7 +11736,7 @@
       </c>
       <c r="J232" s="34"/>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B232, $C$2:$C$695, C232, $D$2:$D$695, D232, $E$2:$E$695, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11794,7 +11782,7 @@
         <v>360</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B233, $C$2:$C$695, C233, $D$2:$D$695, D233, $E$2:$E$695, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O233" s="10"/>
@@ -11842,7 +11830,7 @@
         <v>651</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B234, $C$2:$C$695, C234, $D$2:$D$695, D234, $E$2:$E$695, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O234" s="10"/>
@@ -11890,7 +11878,7 @@
         <v>250</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B235, $C$2:$C$695, C235, $D$2:$D$695, D235, $E$2:$E$695, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11936,13 +11924,13 @@
         <v>650</v>
       </c>
       <c r="N236" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B236, $C$2:$C$695, C236, $D$2:$D$695, D236, $E$2:$E$695, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O236"/>
       <c r="P236"/>
     </row>
-    <row r="237" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A237" s="8" t="s">
         <v>62</v>
       </c>
@@ -11974,7 +11962,7 @@
         <v>118</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B237, $C$2:$C$695, C237, $D$2:$D$695, D237, $E$2:$E$695, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12020,7 +12008,7 @@
         <v>260</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B238, $C$2:$C$695, C238, $D$2:$D$695, D238, $E$2:$E$695, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12066,7 +12054,7 @@
         <v>47480</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B239, $C$2:$C$695, C239, $D$2:$D$695, D239, $E$2:$E$695, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12100,7 +12088,7 @@
       </c>
       <c r="J240" s="34"/>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B240, $C$2:$C$695, C240, $D$2:$D$695, D240, $E$2:$E$695, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12146,7 +12134,7 @@
         <v>300</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B241, $C$2:$C$695, C241, $D$2:$D$695, D241, $E$2:$E$695, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12192,7 +12180,7 @@
         <v>340</v>
       </c>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B242, $C$2:$C$695, C242, $D$2:$D$695, D242, $E$2:$E$695, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12238,7 +12226,7 @@
         <v>1800</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B243, $C$2:$C$695, C243, $D$2:$D$695, D243, $E$2:$E$695, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12272,7 +12260,7 @@
       </c>
       <c r="J244" s="34"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B244, $C$2:$C$695, C244, $D$2:$D$695, D244, $E$2:$E$695, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12311,7 +12299,7 @@
         <v>146</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B245, $C$2:$C$695, C245, $D$2:$D$695, D245, $E$2:$E$695, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12348,7 +12336,7 @@
       <c r="L246" s="18"/>
       <c r="M246" s="18"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B246, $C$2:$C$695, C246, $D$2:$D$695, D246, $E$2:$E$695, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="10"/>
@@ -12396,7 +12384,7 @@
         <v>500</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B247, $C$2:$C$695, C247, $D$2:$D$695, D247, $E$2:$E$695, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="38" t="s">
@@ -12445,7 +12433,7 @@
         <v>300</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B248, $C$2:$C$695, C248, $D$2:$D$695, D248, $E$2:$E$695, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12481,7 +12469,7 @@
         <v>117</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B249, $C$2:$C$695, C249, $D$2:$D$695, D249, $E$2:$E$695, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12520,13 +12508,13 @@
       <c r="L250" s="18"/>
       <c r="M250" s="18"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B250, $C$2:$C$695, C250, $D$2:$D$695, D250, $E$2:$E$695, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="10"/>
       <c r="P250" s="10"/>
     </row>
-    <row r="251" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A251" s="8" t="s">
         <v>62</v>
       </c>
@@ -12554,9 +12542,11 @@
       <c r="I251" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J251" s="34"/>
+      <c r="J251" s="34" t="s">
+        <v>117</v>
+      </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B251, $C$2:$C$695, C251, $D$2:$D$695, D251, $E$2:$E$695, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12602,7 +12592,7 @@
         <v>250</v>
       </c>
       <c r="N252" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B252, $C$2:$C$695, C252, $D$2:$D$695, D252, $E$2:$E$695, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12638,7 +12628,7 @@
         <v>118</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B253, $C$2:$C$695, C253, $D$2:$D$695, D253, $E$2:$E$695, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12684,7 +12674,7 @@
         <v>300</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B254, $C$2:$C$695, C254, $D$2:$D$695, D254, $E$2:$E$695, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12723,7 +12713,7 @@
       <c r="L255" s="18"/>
       <c r="M255" s="18"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B255, $C$2:$C$695, C255, $D$2:$D$695, D255, $E$2:$E$695, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O255" s="10"/>
@@ -12771,7 +12761,7 @@
         <v>400</v>
       </c>
       <c r="N256" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B256, $C$2:$C$695, C256, $D$2:$D$695, D256, $E$2:$E$695, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="10"/>
@@ -12809,7 +12799,7 @@
         <v>118</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B257, $C$2:$C$695, C257, $D$2:$D$695, D257, $E$2:$E$695, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12845,7 +12835,7 @@
         <v>117</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B258, $C$2:$C$695, C258, $D$2:$D$695, D258, $E$2:$E$695, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N300" si="10">IF(COUNTIFS( $B$2:$B$695, B258, $C$2:$C$695, C258, $D$2:$D$695, D258, $E$2:$E$695, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P258" s="29"/>
@@ -12885,7 +12875,7 @@
       <c r="L259" s="18"/>
       <c r="M259" s="18"/>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B259, $C$2:$C$695, C259, $D$2:$D$695, D259, $E$2:$E$695, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="10"/>
@@ -12928,7 +12918,7 @@
       <c r="L260" s="17"/>
       <c r="M260" s="17"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B260, $C$2:$C$695, C260, $D$2:$D$695, D260, $E$2:$E$695, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12962,7 +12952,7 @@
       </c>
       <c r="J261" s="34"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B261, $C$2:$C$695, C261, $D$2:$D$695, D261, $E$2:$E$695, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13008,7 +12998,7 @@
         <v>260</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B262, $C$2:$C$695, C262, $D$2:$D$695, D262, $E$2:$E$695, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O262" s="10"/>
@@ -13049,7 +13039,7 @@
       <c r="L263" s="18"/>
       <c r="M263" s="18"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B263, $C$2:$C$695, C263, $D$2:$D$695, D263, $E$2:$E$695, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="10"/>
@@ -13085,7 +13075,7 @@
       </c>
       <c r="J264" s="34"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B264, $C$2:$C$695, C264, $D$2:$D$695, D264, $E$2:$E$695, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P264" s="29"/>
@@ -13132,11 +13122,11 @@
         <v>300</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B265, $C$2:$C$695, C265, $D$2:$D$695, D265, $E$2:$E$695, E265) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="266" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A266" s="8" t="s">
         <v>62</v>
       </c>
@@ -13164,9 +13154,11 @@
       <c r="I266" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J266" s="34"/>
+      <c r="J266" s="34" t="s">
+        <v>117</v>
+      </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B266, $C$2:$C$695, C266, $D$2:$D$695, D266, $E$2:$E$695, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13200,7 +13192,7 @@
       </c>
       <c r="J267" s="34"/>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B267, $C$2:$C$695, C267, $D$2:$D$695, D267, $E$2:$E$695, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="29"/>
@@ -13237,11 +13229,11 @@
         <v>117</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B268, $C$2:$C$695, C268, $D$2:$D$695, D268, $E$2:$E$695, E268) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="269" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="269" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A269" s="8" t="s">
         <v>62</v>
       </c>
@@ -13269,9 +13261,11 @@
       <c r="I269" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J269" s="34"/>
+      <c r="J269" s="34" t="s">
+        <v>117</v>
+      </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B269, $C$2:$C$695, C269, $D$2:$D$695, D269, $E$2:$E$695, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13307,7 +13301,7 @@
         <v>154</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B270, $C$2:$C$695, C270, $D$2:$D$695, D270, $E$2:$E$695, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13341,7 +13335,7 @@
       </c>
       <c r="J271" s="34"/>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B271, $C$2:$C$695, C271, $D$2:$D$695, D271, $E$2:$E$695, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O271" s="29"/>
@@ -13378,7 +13372,7 @@
         <v>117</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B272, $C$2:$C$695, C272, $D$2:$D$695, D272, $E$2:$E$695, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13424,7 +13418,7 @@
         <v>370</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B273, $C$2:$C$695, C273, $D$2:$D$695, D273, $E$2:$E$695, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P273" s="29"/>
@@ -13471,7 +13465,7 @@
         <v>235</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B274, $C$2:$C$695, C274, $D$2:$D$695, D274, $E$2:$E$695, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13517,7 +13511,7 @@
         <v>285</v>
       </c>
       <c r="N275" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B275, $C$2:$C$695, C275, $D$2:$D$695, D275, $E$2:$E$695, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13563,7 +13557,7 @@
         <v>726</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B276, $C$2:$C$695, C276, $D$2:$D$695, D276, $E$2:$E$695, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13599,11 +13593,11 @@
         <v>117</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B277, $C$2:$C$695, C277, $D$2:$D$695, D277, $E$2:$E$695, E277) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="10"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A278" s="8" t="s">
         <v>62</v>
       </c>
@@ -13635,7 +13629,7 @@
         <v>118</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B278, $C$2:$C$695, C278, $D$2:$D$695, D278, $E$2:$E$695, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13681,7 +13675,7 @@
         <v>300</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B279, $C$2:$C$695, C279, $D$2:$D$695, D279, $E$2:$E$695, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O279" s="10"/>
@@ -13729,7 +13723,7 @@
         <v>275</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B280, $C$2:$C$695, C280, $D$2:$D$695, D280, $E$2:$E$695, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O280" s="10"/>
@@ -13767,7 +13761,7 @@
         <v>117</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B281, $C$2:$C$695, C281, $D$2:$D$695, D281, $E$2:$E$695, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13801,7 +13795,7 @@
       </c>
       <c r="J282" s="34"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B282, $C$2:$C$695, C282, $D$2:$D$695, D282, $E$2:$E$695, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13835,7 +13829,7 @@
       </c>
       <c r="J283" s="34"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B283, $C$2:$C$695, C283, $D$2:$D$695, D283, $E$2:$E$695, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13881,7 +13875,7 @@
         <v>250</v>
       </c>
       <c r="N284" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B284, $C$2:$C$695, C284, $D$2:$D$695, D284, $E$2:$E$695, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P284" s="29"/>
@@ -13916,7 +13910,7 @@
       </c>
       <c r="J285" s="34"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B285, $C$2:$C$695, C285, $D$2:$D$695, D285, $E$2:$E$695, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13950,7 +13944,7 @@
       </c>
       <c r="J286" s="34"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B286, $C$2:$C$695, C286, $D$2:$D$695, D286, $E$2:$E$695, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13996,7 +13990,7 @@
         <v>300</v>
       </c>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B287, $C$2:$C$695, C287, $D$2:$D$695, D287, $E$2:$E$695, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14030,7 +14024,7 @@
       </c>
       <c r="J288" s="34"/>
       <c r="N288" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B288, $C$2:$C$695, C288, $D$2:$D$695, D288, $E$2:$E$695, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P288" s="29"/>
@@ -14067,7 +14061,7 @@
         <v>118</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B289, $C$2:$C$695, C289, $D$2:$D$695, D289, $E$2:$E$695, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14103,7 +14097,7 @@
         <v>118</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B290, $C$2:$C$695, C290, $D$2:$D$695, D290, $E$2:$E$695, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14149,7 +14143,7 @@
         <v>300</v>
       </c>
       <c r="N291" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B291, $C$2:$C$695, C291, $D$2:$D$695, D291, $E$2:$E$695, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14185,7 +14179,7 @@
         <v>118</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B292, $C$2:$C$695, C292, $D$2:$D$695, D292, $E$2:$E$695, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14219,7 +14213,7 @@
       </c>
       <c r="J293" s="34"/>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B293, $C$2:$C$695, C293, $D$2:$D$695, D293, $E$2:$E$695, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14253,7 +14247,7 @@
       </c>
       <c r="J294" s="34"/>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B294, $C$2:$C$695, C294, $D$2:$D$695, D294, $E$2:$E$695, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14287,7 +14281,7 @@
       </c>
       <c r="J295" s="34"/>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B295, $C$2:$C$695, C295, $D$2:$D$695, D295, $E$2:$E$695, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14333,7 +14327,7 @@
         <v>250</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B296, $C$2:$C$695, C296, $D$2:$D$695, D296, $E$2:$E$695, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14369,7 +14363,7 @@
         <v>55</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B297, $C$2:$C$695, C297, $D$2:$D$695, D297, $E$2:$E$695, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14408,7 +14402,7 @@
       <c r="L298" s="27"/>
       <c r="M298" s="27"/>
       <c r="N298" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B298, $C$2:$C$695, C298, $D$2:$D$695, D298, $E$2:$E$695, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O298" s="29"/>
@@ -14449,7 +14443,7 @@
       <c r="L299" s="27"/>
       <c r="M299" s="27"/>
       <c r="N299" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B299, $C$2:$C$695, C299, $D$2:$D$695, D299, $E$2:$E$695, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O299" s="29"/>
@@ -14487,7 +14481,7 @@
         <v>117</v>
       </c>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B300, $C$2:$C$695, C300, $D$2:$D$695, D300, $E$2:$E$695, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22028,9 +22022,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P300" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="RAILTELEQ"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="B"/>
+        <filter val="S"/>
       </filters>
     </filterColumn>
     <filterColumn colId="14">
@@ -22128,7 +22127,7 @@
         <v>30</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" ref="K2:K10" si="2">C3 &amp; " " &amp; D3 &amp; "*" &amp; E3 &amp; " :" &amp; A3</f>
+        <f t="shared" ref="K3:K10" si="2">C3 &amp; " " &amp; D3 &amp; "*" &amp; E3 &amp; " :" &amp; A3</f>
         <v>B 5*1090 :46294.3755324074</v>
       </c>
       <c r="L3">
@@ -22360,7 +22359,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B2, $C$2:$C$695, C2, $D$2:$D$695, D2, $E$2:$E$695, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$695, B2, $C$2:$C$695, C2, $D$2:$D$695, D2, $E$2:$E$695, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -22401,7 +22400,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B3, $C$2:$C$695, C3, $D$2:$D$695, D3, $E$2:$E$695, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22449,7 +22448,7 @@
         <v>34175</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B4, $C$2:$C$695, C4, $D$2:$D$695, D4, $E$2:$E$695, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -22490,7 +22489,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B5, $C$2:$C$695, C5, $D$2:$D$695, D5, $E$2:$E$695, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22531,7 +22530,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B6, $C$2:$C$695, C6, $D$2:$D$695, D6, $E$2:$E$695, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="10"/>
@@ -22570,7 +22569,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B7, $C$2:$C$695, C7, $D$2:$D$695, D7, $E$2:$E$695, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="25"/>
@@ -22609,7 +22608,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B8, $C$2:$C$695, C8, $D$2:$D$695, D8, $E$2:$E$695, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="19"/>
@@ -22650,7 +22649,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B9, $C$2:$C$695, C9, $D$2:$D$695, D9, $E$2:$E$695, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22696,7 +22695,7 @@
         <v>350</v>
       </c>
       <c r="N10" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B10, $C$2:$C$695, C10, $D$2:$D$695, D10, $E$2:$E$695, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O10" s="10"/>
@@ -22735,7 +22734,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B11, $C$2:$C$695, C11, $D$2:$D$695, D11, $E$2:$E$695, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O11" s="10"/>
@@ -22783,7 +22782,7 @@
         <v>500</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B12, $C$2:$C$695, C12, $D$2:$D$695, D12, $E$2:$E$695, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -22824,7 +22823,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B13, $C$2:$C$695, C13, $D$2:$D$695, D13, $E$2:$E$695, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22861,7 +22860,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B14, $C$2:$C$695, C14, $D$2:$D$695, D14, $E$2:$E$695, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -22909,7 +22908,7 @@
         <v>516</v>
       </c>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B15, $C$2:$C$695, C15, $D$2:$D$695, D15, $E$2:$E$695, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22955,7 +22954,7 @@
         <v>300</v>
       </c>
       <c r="N16" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B16, $C$2:$C$695, C16, $D$2:$D$695, D16, $E$2:$E$695, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P16" s="24"/>
@@ -22995,7 +22994,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B17, $C$2:$C$695, C17, $D$2:$D$695, D17, $E$2:$E$695, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23034,7 +23033,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B18, $C$2:$C$695, C18, $D$2:$D$695, D18, $E$2:$E$695, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23073,7 +23072,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B19, $C$2:$C$695, C19, $D$2:$D$695, D19, $E$2:$E$695, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -23121,7 +23120,7 @@
         <v>300</v>
       </c>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B20, $C$2:$C$695, C20, $D$2:$D$695, D20, $E$2:$E$695, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23163,7 +23162,7 @@
         <v>3156</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B21, $C$2:$C$695, C21, $D$2:$D$695, D21, $E$2:$E$695, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -23202,7 +23201,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B22, $C$2:$C$695, C22, $D$2:$D$695, D22, $E$2:$E$695, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -23240,7 +23239,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B23, $C$2:$C$695, C23, $D$2:$D$695, D23, $E$2:$E$695, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -23281,7 +23280,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B24, $C$2:$C$695, C24, $D$2:$D$695, D24, $E$2:$E$695, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -23330,7 +23329,7 @@
         <v>225</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B25, $C$2:$C$695, C25, $D$2:$D$695, D25, $E$2:$E$695, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23369,7 +23368,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B26, $C$2:$C$695, C26, $D$2:$D$695, D26, $E$2:$E$695, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P26"/>
@@ -23409,7 +23408,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B27, $C$2:$C$695, C27, $D$2:$D$695, D27, $E$2:$E$695, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23448,7 +23447,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B28, $C$2:$C$695, C28, $D$2:$D$695, D28, $E$2:$E$695, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -23487,7 +23486,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B29, $C$2:$C$695, C29, $D$2:$D$695, D29, $E$2:$E$695, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -23527,7 +23526,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B30, $C$2:$C$695, C30, $D$2:$D$695, D30, $E$2:$E$695, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -23568,7 +23567,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="17"/>
       <c r="N31" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B31, $C$2:$C$695, C31, $D$2:$D$695, D31, $E$2:$E$695, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O31"/>
@@ -23609,7 +23608,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B32, $C$2:$C$695, C32, $D$2:$D$695, D32, $E$2:$E$695, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -23650,7 +23649,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B33, $C$2:$C$695, C33, $D$2:$D$695, D33, $E$2:$E$695, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -23689,7 +23688,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B34, $C$2:$C$695, C34, $D$2:$D$695, D34, $E$2:$E$695, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -23730,7 +23729,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B35, $C$2:$C$695, C35, $D$2:$D$695, D35, $E$2:$E$695, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O35"/>
@@ -23778,7 +23777,7 @@
         <v>300</v>
       </c>
       <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B36, $C$2:$C$695, C36, $D$2:$D$695, D36, $E$2:$E$695, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -23819,7 +23818,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B37, $C$2:$C$695, C37, $D$2:$D$695, D37, $E$2:$E$695, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -23867,7 +23866,7 @@
         <v>314</v>
       </c>
       <c r="N38" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B38, $C$2:$C$695, C38, $D$2:$D$695, D38, $E$2:$E$695, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23904,7 +23903,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B39, $C$2:$C$695, C39, $D$2:$D$695, D39, $E$2:$E$695, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -23952,7 +23951,7 @@
         <v>646</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B40, $C$2:$C$695, C40, $D$2:$D$695, D40, $E$2:$E$695, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23989,7 +23988,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B41, $C$2:$C$695, C41, $D$2:$D$695, D41, $E$2:$E$695, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -24037,7 +24036,7 @@
         <v>240</v>
       </c>
       <c r="N42" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B42, $C$2:$C$695, C42, $D$2:$D$695, D42, $E$2:$E$695, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24076,7 +24075,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B43, $C$2:$C$695, C43, $D$2:$D$695, D43, $E$2:$E$695, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -24119,7 +24118,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B44, $C$2:$C$695, C44, $D$2:$D$695, D44, $E$2:$E$695, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -24158,7 +24157,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B45, $C$2:$C$695, C45, $D$2:$D$695, D45, $E$2:$E$695, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -24197,7 +24196,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B46, $C$2:$C$695, C46, $D$2:$D$695, D46, $E$2:$E$695, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -24236,7 +24235,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B47, $C$2:$C$695, C47, $D$2:$D$695, D47, $E$2:$E$695, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -24285,7 +24284,7 @@
         <v>540</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B48, $C$2:$C$695, C48, $D$2:$D$695, D48, $E$2:$E$695, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24322,7 +24321,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="17"/>
       <c r="N49" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B49, $C$2:$C$695, C49, $D$2:$D$695, D49, $E$2:$E$695, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24368,7 +24367,7 @@
         <v>302</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B50, $C$2:$C$695, C50, $D$2:$D$695, D50, $E$2:$E$695, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="10"/>
@@ -24407,7 +24406,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B51, $C$2:$C$695, C51, $D$2:$D$695, D51, $E$2:$E$695, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24453,7 +24452,7 @@
         <v>250</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B52, $C$2:$C$695, C52, $D$2:$D$695, D52, $E$2:$E$695, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -24492,7 +24491,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B53, $C$2:$C$695, C53, $D$2:$D$695, D53, $E$2:$E$695, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24529,7 +24528,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B54, $C$2:$C$695, C54, $D$2:$D$695, D54, $E$2:$E$695, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -24568,7 +24567,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B55, $C$2:$C$695, C55, $D$2:$D$695, D55, $E$2:$E$695, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -24616,7 +24615,7 @@
         <v>10680</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B56, $C$2:$C$695, C56, $D$2:$D$695, D56, $E$2:$E$695, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="10"/>
@@ -24657,7 +24656,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B57, $C$2:$C$695, C57, $D$2:$D$695, D57, $E$2:$E$695, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -24696,7 +24695,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B58, $C$2:$C$695, C58, $D$2:$D$695, D58, $E$2:$E$695, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -24735,7 +24734,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B59, $C$2:$C$695, C59, $D$2:$D$695, D59, $E$2:$E$695, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
@@ -24783,7 +24782,7 @@
         <v>500</v>
       </c>
       <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B60, $C$2:$C$695, C60, $D$2:$D$695, D60, $E$2:$E$695, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24829,7 +24828,7 @@
         <v>720</v>
       </c>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B61, $C$2:$C$695, C61, $D$2:$D$695, D61, $E$2:$E$695, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24875,7 +24874,7 @@
         <v>10880</v>
       </c>
       <c r="N62" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B62, $C$2:$C$695, C62, $D$2:$D$695, D62, $E$2:$E$695, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24914,7 +24913,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B63, $C$2:$C$695, C63, $D$2:$D$695, D63, $E$2:$E$695, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O63"/>
@@ -24955,7 +24954,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B64, $C$2:$C$695, C64, $D$2:$D$695, D64, $E$2:$E$695, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -25004,7 +25003,7 @@
         <v>200</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B65, $C$2:$C$695, C65, $D$2:$D$695, D65, $E$2:$E$695, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25043,7 +25042,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B66, $C$2:$C$695, C66, $D$2:$D$695, D66, $E$2:$E$695, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$695, B66, $C$2:$C$695, C66, $D$2:$D$695, D66, $E$2:$E$695, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O66"/>
@@ -25091,7 +25090,7 @@
         <v>1200</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B67, $C$2:$C$695, C67, $D$2:$D$695, D67, $E$2:$E$695, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O67" s="38" t="s">
@@ -25133,7 +25132,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B68, $C$2:$C$695, C68, $D$2:$D$695, D68, $E$2:$E$695, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68"/>
@@ -25174,7 +25173,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="17"/>
       <c r="N69" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B69, $C$2:$C$695, C69, $D$2:$D$695, D69, $E$2:$E$695, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69"/>
@@ -25219,11 +25218,11 @@
         <v>8870</v>
       </c>
       <c r="M70" s="18">
-        <f t="shared" ref="M70:M77" si="0">ABS((D70*E70)-L70)</f>
+        <f t="shared" ref="M70:M77" si="2">ABS((D70*E70)-L70)</f>
         <v>300</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B70, $C$2:$C$695, C70, $D$2:$D$695, D70, $E$2:$E$695, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25265,11 +25264,11 @@
         <v>4640</v>
       </c>
       <c r="M71" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B71, $C$2:$C$695, C71, $D$2:$D$695, D71, $E$2:$E$695, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O71" s="38" t="s">
@@ -25315,11 +25314,11 @@
         <v>11360</v>
       </c>
       <c r="M72" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B72, $C$2:$C$695, C72, $D$2:$D$695, D72, $E$2:$E$695, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25361,11 +25360,11 @@
         <v>8320</v>
       </c>
       <c r="M73" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B73, $C$2:$C$695, C73, $D$2:$D$695, D73, $E$2:$E$695, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25407,11 +25406,11 @@
         <v>32900</v>
       </c>
       <c r="M74" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1000</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B74, $C$2:$C$695, C74, $D$2:$D$695, D74, $E$2:$E$695, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25453,11 +25452,11 @@
         <v>4510</v>
       </c>
       <c r="M75" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>288</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B75, $C$2:$C$695, C75, $D$2:$D$695, D75, $E$2:$E$695, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25499,11 +25498,11 @@
         <v>15300</v>
       </c>
       <c r="M76" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>420</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B76, $C$2:$C$695, C76, $D$2:$D$695, D76, $E$2:$E$695, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25546,11 +25545,11 @@
         <v>8970</v>
       </c>
       <c r="M77" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B77, $C$2:$C$695, C77, $D$2:$D$695, D77, $E$2:$E$695, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25587,7 +25586,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="17"/>
       <c r="N78" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B78, $C$2:$C$695, C78, $D$2:$D$695, D78, $E$2:$E$695, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78"/>
@@ -25631,11 +25630,11 @@
         <v>16755</v>
       </c>
       <c r="M79" s="18">
-        <f t="shared" ref="M79:M97" si="1">ABS((D79*E79)-L79)</f>
+        <f t="shared" ref="M79:M97" si="3">ABS((D79*E79)-L79)</f>
         <v>295</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B79, $C$2:$C$695, C79, $D$2:$D$695, D79, $E$2:$E$695, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O79" s="10"/>
@@ -25679,11 +25678,11 @@
         <v>8220</v>
       </c>
       <c r="M80" s="18">
+        <f t="shared" si="3"/>
+        <v>360</v>
+      </c>
+      <c r="N80" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B80, $C$2:$C$695, C80, $D$2:$D$695, D80, $E$2:$E$695, E80) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O80" s="38" t="s">
@@ -25728,11 +25727,11 @@
         <v>10250</v>
       </c>
       <c r="M81" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N81" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B81, $C$2:$C$695, C81, $D$2:$D$695, D81, $E$2:$E$695, E81) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25774,11 +25773,11 @@
         <v>19550</v>
       </c>
       <c r="M82" s="18">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="N82" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-      <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B82, $C$2:$C$695, C82, $D$2:$D$695, D82, $E$2:$E$695, E82) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25820,11 +25819,11 @@
         <v>39300</v>
       </c>
       <c r="M83" s="18">
+        <f t="shared" si="3"/>
+        <v>18850</v>
+      </c>
+      <c r="N83" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>18850</v>
-      </c>
-      <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B83, $C$2:$C$695, C83, $D$2:$D$695, D83, $E$2:$E$695, E83) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25866,11 +25865,11 @@
         <v>33200</v>
       </c>
       <c r="M84" s="18">
+        <f t="shared" si="3"/>
+        <v>1200</v>
+      </c>
+      <c r="N84" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-      <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B84, $C$2:$C$695, C84, $D$2:$D$695, D84, $E$2:$E$695, E84) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25912,11 +25911,11 @@
         <v>9170</v>
       </c>
       <c r="M85" s="27">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="N85" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B85, $C$2:$C$695, C85, $D$2:$D$695, D85, $E$2:$E$695, E85) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O85" s="38" t="s">
@@ -25961,11 +25960,11 @@
         <v>10400</v>
       </c>
       <c r="M86" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N86" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B86, $C$2:$C$695, C86, $D$2:$D$695, D86, $E$2:$E$695, E86) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26007,11 +26006,11 @@
         <v>8420</v>
       </c>
       <c r="M87" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N87" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B87, $C$2:$C$695, C87, $D$2:$D$695, D87, $E$2:$E$695, E87) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26053,11 +26052,11 @@
         <v>6202</v>
       </c>
       <c r="M88" s="18">
+        <f t="shared" si="3"/>
+        <v>496</v>
+      </c>
+      <c r="N88" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>496</v>
-      </c>
-      <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B88, $C$2:$C$695, C88, $D$2:$D$695, D88, $E$2:$E$695, E88) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26099,11 +26098,11 @@
         <v>3560</v>
       </c>
       <c r="M89" s="18">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="N89" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B89, $C$2:$C$695, C89, $D$2:$D$695, D89, $E$2:$E$695, E89) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26145,11 +26144,11 @@
         <v>11660</v>
       </c>
       <c r="M90" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N90" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B90, $C$2:$C$695, C90, $D$2:$D$695, D90, $E$2:$E$695, E90) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O90" s="38" t="s">
@@ -26195,11 +26194,11 @@
         <v>19730.5</v>
       </c>
       <c r="M91" s="27">
+        <f t="shared" si="3"/>
+        <v>504.5</v>
+      </c>
+      <c r="N91" s="29" t="str">
         <f t="shared" si="1"/>
-        <v>504.5</v>
-      </c>
-      <c r="N91" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B91, $C$2:$C$695, C91, $D$2:$D$695, D91, $E$2:$E$695, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O91" s="38" t="s">
@@ -26245,11 +26244,11 @@
         <v>19690</v>
       </c>
       <c r="M92" s="27">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+      <c r="N92" s="29" t="str">
         <f t="shared" si="1"/>
-        <v>545</v>
-      </c>
-      <c r="N92" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B92, $C$2:$C$695, C92, $D$2:$D$695, D92, $E$2:$E$695, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="38" t="s">
@@ -26295,11 +26294,11 @@
         <v>9886</v>
       </c>
       <c r="M93" s="18">
+        <f t="shared" si="3"/>
+        <v>654</v>
+      </c>
+      <c r="N93" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>654</v>
-      </c>
-      <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B93, $C$2:$C$695, C93, $D$2:$D$695, D93, $E$2:$E$695, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26341,11 +26340,11 @@
         <v>9170</v>
       </c>
       <c r="M94" s="27">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N94" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B94, $C$2:$C$695, C94, $D$2:$D$695, D94, $E$2:$E$695, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26387,11 +26386,11 @@
         <v>33950</v>
       </c>
       <c r="M95" s="18">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
+      <c r="N95" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B95, $C$2:$C$695, C95, $D$2:$D$695, D95, $E$2:$E$695, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O95" s="10"/>
@@ -26435,11 +26434,11 @@
         <v>8570</v>
       </c>
       <c r="M96" s="27">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+      <c r="N96" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-      <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B96, $C$2:$C$695, C96, $D$2:$D$695, D96, $E$2:$E$695, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O96" s="38" t="s">
@@ -26484,11 +26483,11 @@
         <v>17150</v>
       </c>
       <c r="M97" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N97" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B97, $C$2:$C$695, C97, $D$2:$D$695, D97, $E$2:$E$695, E97) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26524,7 +26523,7 @@
         <v>117</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B98, $C$2:$C$695, C98, $D$2:$D$695, D98, $E$2:$E$695, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26570,7 +26569,7 @@
         <v>250</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B99, $C$2:$C$695, C99, $D$2:$D$695, D99, $E$2:$E$695, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26616,7 +26615,7 @@
         <v>300.80000000000018</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B100, $C$2:$C$695, C100, $D$2:$D$695, D100, $E$2:$E$695, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="38" t="s">
@@ -26666,7 +26665,7 @@
         <v>235</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B101, $C$2:$C$695, C101, $D$2:$D$695, D101, $E$2:$E$695, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26712,7 +26711,7 @@
         <v>4451</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B102, $C$2:$C$695, C102, $D$2:$D$695, D102, $E$2:$E$695, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O102" s="38" t="s">
@@ -26761,7 +26760,7 @@
         <v>714</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B103, $C$2:$C$695, C103, $D$2:$D$695, D103, $E$2:$E$695, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26800,7 +26799,7 @@
       <c r="L104" s="17"/>
       <c r="M104" s="17"/>
       <c r="N104" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B104, $C$2:$C$695, C104, $D$2:$D$695, D104, $E$2:$E$695, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O104"/>
@@ -26848,7 +26847,7 @@
         <v>450</v>
       </c>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B105, $C$2:$C$695, C105, $D$2:$D$695, D105, $E$2:$E$695, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P105"/>
@@ -26895,7 +26894,7 @@
         <v>270</v>
       </c>
       <c r="N106" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B106, $C$2:$C$695, C106, $D$2:$D$695, D106, $E$2:$E$695, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="39" t="s">
@@ -26945,7 +26944,7 @@
         <v>188.60000000000014</v>
       </c>
       <c r="N107" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B107, $C$2:$C$695, C107, $D$2:$D$695, D107, $E$2:$E$695, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="39" t="s">
@@ -26995,7 +26994,7 @@
         <v>300</v>
       </c>
       <c r="N108" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B108, $C$2:$C$695, C108, $D$2:$D$695, D108, $E$2:$E$695, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108" s="10"/>
@@ -27043,7 +27042,7 @@
         <v>18350</v>
       </c>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B109, $C$2:$C$695, C109, $D$2:$D$695, D109, $E$2:$E$695, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="10"/>
@@ -27081,7 +27080,7 @@
         <v>118</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B110, $C$2:$C$695, C110, $D$2:$D$695, D110, $E$2:$E$695, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27127,7 +27126,7 @@
         <v>300</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B111, $C$2:$C$695, C111, $D$2:$D$695, D111, $E$2:$E$695, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27173,7 +27172,7 @@
         <v>395</v>
       </c>
       <c r="N112" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B112, $C$2:$C$695, C112, $D$2:$D$695, D112, $E$2:$E$695, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O112" s="38" t="s">
@@ -27223,7 +27222,7 @@
         <v>250</v>
       </c>
       <c r="N113" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B113, $C$2:$C$695, C113, $D$2:$D$695, D113, $E$2:$E$695, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O113" s="38" t="s">
@@ -27273,7 +27272,7 @@
         <v>300</v>
       </c>
       <c r="N114" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B114, $C$2:$C$695, C114, $D$2:$D$695, D114, $E$2:$E$695, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O114"/>
@@ -27321,7 +27320,7 @@
         <v>645</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B115, $C$2:$C$695, C115, $D$2:$D$695, D115, $E$2:$E$695, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O115" s="38" t="s">
@@ -27363,7 +27362,7 @@
         <v>145</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B116, $C$2:$C$695, C116, $D$2:$D$695, D116, $E$2:$E$695, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27409,7 +27408,7 @@
         <v>300</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B117, $C$2:$C$695, C117, $D$2:$D$695, D117, $E$2:$E$695, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="38" t="s">
@@ -27459,7 +27458,7 @@
         <v>1400</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B118, $C$2:$C$695, C118, $D$2:$D$695, D118, $E$2:$E$695, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="38" t="s">
@@ -27496,7 +27495,7 @@
       </c>
       <c r="J119" s="34"/>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B119, $C$2:$C$695, C119, $D$2:$D$695, D119, $E$2:$E$695, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27542,7 +27541,7 @@
         <v>290</v>
       </c>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B120, $C$2:$C$695, C120, $D$2:$D$695, D120, $E$2:$E$695, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27588,7 +27587,7 @@
         <v>280</v>
       </c>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B121, $C$2:$C$695, C121, $D$2:$D$695, D121, $E$2:$E$695, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="38" t="s">
@@ -27626,7 +27625,7 @@
       </c>
       <c r="J122" s="34"/>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B122, $C$2:$C$695, C122, $D$2:$D$695, D122, $E$2:$E$695, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27672,7 +27671,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B123, $C$2:$C$695, C123, $D$2:$D$695, D123, $E$2:$E$695, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P123"/>
@@ -27719,7 +27718,7 @@
         <v>650</v>
       </c>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B124, $C$2:$C$695, C124, $D$2:$D$695, D124, $E$2:$E$695, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27765,7 +27764,7 @@
         <v>275</v>
       </c>
       <c r="N125" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B125, $C$2:$C$695, C125, $D$2:$D$695, D125, $E$2:$E$695, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -27811,7 +27810,7 @@
         <v>225</v>
       </c>
       <c r="N126" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B126, $C$2:$C$695, C126, $D$2:$D$695, D126, $E$2:$E$695, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O126" s="10"/>
@@ -27852,7 +27851,7 @@
       <c r="L127" s="17"/>
       <c r="M127" s="17"/>
       <c r="N127" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B127, $C$2:$C$695, C127, $D$2:$D$695, D127, $E$2:$E$695, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127"/>
@@ -27888,7 +27887,7 @@
       </c>
       <c r="J128" s="34"/>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B128, $C$2:$C$695, C128, $D$2:$D$695, D128, $E$2:$E$695, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="38" t="s">
@@ -27938,7 +27937,7 @@
         <v>500</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B129, $C$2:$C$695, C129, $D$2:$D$695, D129, $E$2:$E$695, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27984,7 +27983,7 @@
         <v>320</v>
       </c>
       <c r="N130" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B130, $C$2:$C$695, C130, $D$2:$D$695, D130, $E$2:$E$695, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="4">IF(COUNTIFS( $B$2:$B$695, B130, $C$2:$C$695, C130, $D$2:$D$695, D130, $E$2:$E$695, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="29"/>
@@ -28032,7 +28031,7 @@
         <v>235</v>
       </c>
       <c r="N131" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B131, $C$2:$C$695, C131, $D$2:$D$695, D131, $E$2:$E$695, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="29"/>
@@ -28068,7 +28067,7 @@
       </c>
       <c r="J132" s="34"/>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B132, $C$2:$C$695, C132, $D$2:$D$695, D132, $E$2:$E$695, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O132" s="29"/>
@@ -28111,11 +28110,11 @@
         <v>10300</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" ref="M133:M138" si="2">ABS((D133*E133)-L133)</f>
+        <f t="shared" ref="M133:M138" si="5">ABS((D133*E133)-L133)</f>
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B133, $C$2:$C$695, C133, $D$2:$D$695, D133, $E$2:$E$695, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P133" s="29"/>
@@ -28158,11 +28157,11 @@
         <v>16580</v>
       </c>
       <c r="M134" s="44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>660</v>
       </c>
       <c r="N134" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B134, $C$2:$C$695, C134, $D$2:$D$695, D134, $E$2:$E$695, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="24"/>
@@ -28208,11 +28207,11 @@
         <v>8820</v>
       </c>
       <c r="M135" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N135" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B135, $C$2:$C$695, C135, $D$2:$D$695, D135, $E$2:$E$695, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="29"/>
@@ -28256,11 +28255,11 @@
         <v>36946</v>
       </c>
       <c r="M136" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>934</v>
       </c>
       <c r="N136" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B136, $C$2:$C$695, C136, $D$2:$D$695, D136, $E$2:$E$695, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="29"/>
@@ -28304,11 +28303,11 @@
         <v>34100</v>
       </c>
       <c r="M137" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1700</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B137, $C$2:$C$695, C137, $D$2:$D$695, D137, $E$2:$E$695, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="29"/>
@@ -28351,11 +28350,11 @@
         <v>14200</v>
       </c>
       <c r="M138" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>500</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B138, $C$2:$C$695, C138, $D$2:$D$695, D138, $E$2:$E$695, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28392,7 +28391,7 @@
       <c r="L139" s="18"/>
       <c r="M139" s="18"/>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B139, $C$2:$C$695, C139, $D$2:$D$695, D139, $E$2:$E$695, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O139" s="24"/>
@@ -28440,7 +28439,7 @@
         <v>300</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B140, $C$2:$C$695, C140, $D$2:$D$695, D140, $E$2:$E$695, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="10"/>
@@ -28488,7 +28487,7 @@
         <v>250</v>
       </c>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B141, $C$2:$C$695, C141, $D$2:$D$695, D141, $E$2:$E$695, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28524,7 +28523,7 @@
         <v>118</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B142, $C$2:$C$695, C142, $D$2:$D$695, D142, $E$2:$E$695, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28570,7 +28569,7 @@
         <v>300</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B143, $C$2:$C$695, C143, $D$2:$D$695, D143, $E$2:$E$695, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="29"/>
@@ -28617,7 +28616,7 @@
         <v>300</v>
       </c>
       <c r="N144" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B144, $C$2:$C$695, C144, $D$2:$D$695, D144, $E$2:$E$695, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28651,7 +28650,7 @@
       </c>
       <c r="J145" s="34"/>
       <c r="N145" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B145, $C$2:$C$695, C145, $D$2:$D$695, D145, $E$2:$E$695, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28685,7 +28684,7 @@
       </c>
       <c r="J146" s="34"/>
       <c r="N146" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B146, $C$2:$C$695, C146, $D$2:$D$695, D146, $E$2:$E$695, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28731,7 +28730,7 @@
         <v>500</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B147, $C$2:$C$695, C147, $D$2:$D$695, D147, $E$2:$E$695, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O147" s="39" t="s">
@@ -28768,7 +28767,7 @@
       </c>
       <c r="J148" s="34"/>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B148, $C$2:$C$695, C148, $D$2:$D$695, D148, $E$2:$E$695, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28814,7 +28813,7 @@
         <v>501</v>
       </c>
       <c r="N149" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B149, $C$2:$C$695, C149, $D$2:$D$695, D149, $E$2:$E$695, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="38" t="s">
@@ -28863,7 +28862,7 @@
         <v>300</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B150, $C$2:$C$695, C150, $D$2:$D$695, D150, $E$2:$E$695, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="10"/>
@@ -28911,7 +28910,7 @@
         <v>810</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B151, $C$2:$C$695, C151, $D$2:$D$695, D151, $E$2:$E$695, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O151" s="10"/>
@@ -28949,7 +28948,7 @@
         <v>118</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B152, $C$2:$C$695, C152, $D$2:$D$695, D152, $E$2:$E$695, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28991,11 +28990,11 @@
         <v>14400</v>
       </c>
       <c r="M153" s="18">
-        <f t="shared" ref="M153:M158" si="3">ABS((D153*E153)-L153)</f>
+        <f t="shared" ref="M153:M158" si="6">ABS((D153*E153)-L153)</f>
         <v>500</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B153, $C$2:$C$695, C153, $D$2:$D$695, D153, $E$2:$E$695, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29037,11 +29036,11 @@
         <v>37480</v>
       </c>
       <c r="M154" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1000</v>
       </c>
       <c r="N154" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B154, $C$2:$C$695, C154, $D$2:$D$695, D154, $E$2:$E$695, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P154" s="29"/>
@@ -29084,11 +29083,11 @@
         <v>14440</v>
       </c>
       <c r="M155" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B155, $C$2:$C$695, C155, $D$2:$D$695, D155, $E$2:$E$695, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O155"/>
@@ -29131,11 +29130,11 @@
         <v>10510</v>
       </c>
       <c r="M156" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B156, $C$2:$C$695, C156, $D$2:$D$695, D156, $E$2:$E$695, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29177,11 +29176,11 @@
         <v>5905</v>
       </c>
       <c r="M157" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>275</v>
       </c>
       <c r="N157" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B157, $C$2:$C$695, C157, $D$2:$D$695, D157, $E$2:$E$695, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29223,11 +29222,11 @@
         <v>8700</v>
       </c>
       <c r="M158" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B158, $C$2:$C$695, C158, $D$2:$D$695, D158, $E$2:$E$695, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29261,7 +29260,7 @@
       </c>
       <c r="J159" s="34"/>
       <c r="N159" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B159, $C$2:$C$695, C159, $D$2:$D$695, D159, $E$2:$E$695, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P159" s="29"/>
@@ -29298,7 +29297,7 @@
         <v>118</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B160, $C$2:$C$695, C160, $D$2:$D$695, D160, $E$2:$E$695, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P160"/>
@@ -29333,7 +29332,7 @@
       </c>
       <c r="J161" s="34"/>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B161, $C$2:$C$695, C161, $D$2:$D$695, D161, $E$2:$E$695, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29372,7 +29371,7 @@
       <c r="L162" s="18"/>
       <c r="M162" s="18"/>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B162, $C$2:$C$695, C162, $D$2:$D$695, D162, $E$2:$E$695, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O162" s="10"/>
@@ -29420,7 +29419,7 @@
         <v>250</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B163, $C$2:$C$695, C163, $D$2:$D$695, D163, $E$2:$E$695, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29466,7 +29465,7 @@
         <v>300</v>
       </c>
       <c r="N164" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B164, $C$2:$C$695, C164, $D$2:$D$695, D164, $E$2:$E$695, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O164" s="38" t="s">
@@ -29515,7 +29514,7 @@
         <v>253</v>
       </c>
       <c r="N165" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B165, $C$2:$C$695, C165, $D$2:$D$695, D165, $E$2:$E$695, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O165" s="38" t="s">
@@ -29564,7 +29563,7 @@
         <v>355.5</v>
       </c>
       <c r="N166" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B166, $C$2:$C$695, C166, $D$2:$D$695, D166, $E$2:$E$695, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="O166" s="38" t="s">
@@ -29614,7 +29613,7 @@
         <v>300</v>
       </c>
       <c r="N167" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B167, $C$2:$C$695, C167, $D$2:$D$695, D167, $E$2:$E$695, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O167" s="10"/>
@@ -29652,7 +29651,7 @@
         <v>117</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B168, $C$2:$C$695, C168, $D$2:$D$695, D168, $E$2:$E$695, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29698,7 +29697,7 @@
         <v>48320</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B169, $C$2:$C$695, C169, $D$2:$D$695, D169, $E$2:$E$695, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="38" t="s">
@@ -29747,7 +29746,7 @@
         <v>300</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B170, $C$2:$C$695, C170, $D$2:$D$695, D170, $E$2:$E$695, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29793,7 +29792,7 @@
         <v>480</v>
       </c>
       <c r="N171" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B171, $C$2:$C$695, C171, $D$2:$D$695, D171, $E$2:$E$695, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29839,7 +29838,7 @@
         <v>300</v>
       </c>
       <c r="N172" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B172, $C$2:$C$695, C172, $D$2:$D$695, D172, $E$2:$E$695, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O172" s="29"/>
@@ -29887,7 +29886,7 @@
         <v>188</v>
       </c>
       <c r="N173" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B173, $C$2:$C$695, C173, $D$2:$D$695, D173, $E$2:$E$695, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O173" s="29"/>
@@ -29923,7 +29922,7 @@
       </c>
       <c r="J174" s="34"/>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B174, $C$2:$C$695, C174, $D$2:$D$695, D174, $E$2:$E$695, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29969,7 +29968,7 @@
         <v>294</v>
       </c>
       <c r="N175" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B175, $C$2:$C$695, C175, $D$2:$D$695, D175, $E$2:$E$695, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30015,7 +30014,7 @@
         <v>294</v>
       </c>
       <c r="N176" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B176, $C$2:$C$695, C176, $D$2:$D$695, D176, $E$2:$E$695, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30061,7 +30060,7 @@
         <v>280</v>
       </c>
       <c r="N177" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B177, $C$2:$C$695, C177, $D$2:$D$695, D177, $E$2:$E$695, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="29"/>
@@ -30109,7 +30108,7 @@
         <v>940</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B178, $C$2:$C$695, C178, $D$2:$D$695, D178, $E$2:$E$695, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30155,7 +30154,7 @@
         <v>450</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B179, $C$2:$C$695, C179, $D$2:$D$695, D179, $E$2:$E$695, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30191,7 +30190,7 @@
         <v>118</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B180, $C$2:$C$695, C180, $D$2:$D$695, D180, $E$2:$E$695, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="38" t="s">
@@ -30230,7 +30229,7 @@
         <v>195</v>
       </c>
       <c r="N181" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B181, $C$2:$C$695, C181, $D$2:$D$695, D181, $E$2:$E$695, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30276,7 +30275,7 @@
         <v>150</v>
       </c>
       <c r="N182" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B182, $C$2:$C$695, C182, $D$2:$D$695, D182, $E$2:$E$695, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30322,7 +30321,7 @@
         <v>250</v>
       </c>
       <c r="N183" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B183, $C$2:$C$695, C183, $D$2:$D$695, D183, $E$2:$E$695, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30368,7 +30367,7 @@
         <v>527.5</v>
       </c>
       <c r="N184" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B184, $C$2:$C$695, C184, $D$2:$D$695, D184, $E$2:$E$695, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="29"/>
@@ -30411,7 +30410,7 @@
       <c r="L185" s="27"/>
       <c r="M185" s="27"/>
       <c r="N185" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B185, $C$2:$C$695, C185, $D$2:$D$695, D185, $E$2:$E$695, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O185" s="29"/>
@@ -30452,7 +30451,7 @@
       <c r="L186" s="18"/>
       <c r="M186" s="18"/>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B186, $C$2:$C$695, C186, $D$2:$D$695, D186, $E$2:$E$695, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O186" s="10"/>
@@ -30500,7 +30499,7 @@
         <v>140</v>
       </c>
       <c r="N187" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B187, $C$2:$C$695, C187, $D$2:$D$695, D187, $E$2:$E$695, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
       <c r="P187" s="29"/>
@@ -30547,7 +30546,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B188, $C$2:$C$695, C188, $D$2:$D$695, D188, $E$2:$E$695, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30593,7 +30592,7 @@
         <v>800</v>
       </c>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B189, $C$2:$C$695, C189, $D$2:$D$695, D189, $E$2:$E$695, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O189" s="38" t="s">
@@ -30635,7 +30634,7 @@
       <c r="L190" s="44"/>
       <c r="M190" s="44"/>
       <c r="N190" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B190, $C$2:$C$695, C190, $D$2:$D$695, D190, $E$2:$E$695, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="24"/>
@@ -30685,7 +30684,7 @@
         <v>300</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B191, $C$2:$C$695, C191, $D$2:$D$695, D191, $E$2:$E$695, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
       <c r="P191" s="25"/>
@@ -30732,7 +30731,7 @@
         <v>250</v>
       </c>
       <c r="N192" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B192, $C$2:$C$695, C192, $D$2:$D$695, D192, $E$2:$E$695, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30768,7 +30767,7 @@
         <v>117</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B193, $C$2:$C$695, C193, $D$2:$D$695, D193, $E$2:$E$695, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="4"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30814,7 +30813,7 @@
         <v>880</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B194, $C$2:$C$695, C194, $D$2:$D$695, D194, $E$2:$E$695, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="7">IF(COUNTIFS( $B$2:$B$695, B194, $C$2:$C$695, C194, $D$2:$D$695, D194, $E$2:$E$695, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="38" t="s">
@@ -30854,7 +30853,7 @@
       <c r="L195" s="18"/>
       <c r="M195" s="18"/>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B195, $C$2:$C$695, C195, $D$2:$D$695, D195, $E$2:$E$695, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O195" s="10"/>
@@ -30902,7 +30901,7 @@
         <v>290</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B196, $C$2:$C$695, C196, $D$2:$D$695, D196, $E$2:$E$695, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30938,7 +30937,7 @@
         <v>117</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B197, $C$2:$C$695, C197, $D$2:$D$695, D197, $E$2:$E$695, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30972,7 +30971,7 @@
       </c>
       <c r="J198" s="34"/>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B198, $C$2:$C$695, C198, $D$2:$D$695, D198, $E$2:$E$695, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31008,7 +31007,7 @@
         <v>118</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B199, $C$2:$C$695, C199, $D$2:$D$695, D199, $E$2:$E$695, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="29"/>
@@ -31055,7 +31054,7 @@
         <v>47900</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B200, $C$2:$C$695, C200, $D$2:$D$695, D200, $E$2:$E$695, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O200" s="38" t="s">
@@ -31104,7 +31103,7 @@
         <v>650</v>
       </c>
       <c r="N201" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B201, $C$2:$C$695, C201, $D$2:$D$695, D201, $E$2:$E$695, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P201" s="29"/>
@@ -31151,7 +31150,7 @@
         <v>646</v>
       </c>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B202, $C$2:$C$695, C202, $D$2:$D$695, D202, $E$2:$E$695, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O202" s="38" t="s">
@@ -31190,7 +31189,7 @@
         <v>118</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B203, $C$2:$C$695, C203, $D$2:$D$695, D203, $E$2:$E$695, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O203" s="29"/>
@@ -31237,7 +31236,7 @@
         <v>650</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B204, $C$2:$C$695, C204, $D$2:$D$695, D204, $E$2:$E$695, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="38" t="s">
@@ -31286,7 +31285,7 @@
         <v>495</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B205, $C$2:$C$695, C205, $D$2:$D$695, D205, $E$2:$E$695, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O205" s="38" t="s">
@@ -31325,7 +31324,7 @@
         <v>55</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B206, $C$2:$C$695, C206, $D$2:$D$695, D206, $E$2:$E$695, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31371,7 +31370,7 @@
         <v>816</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B207, $C$2:$C$695, C207, $D$2:$D$695, D207, $E$2:$E$695, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31417,7 +31416,7 @@
         <v>250</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B208, $C$2:$C$695, C208, $D$2:$D$695, D208, $E$2:$E$695, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31463,7 +31462,7 @@
         <v>300</v>
       </c>
       <c r="N209" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B209, $C$2:$C$695, C209, $D$2:$D$695, D209, $E$2:$E$695, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31509,7 +31508,7 @@
         <v>300</v>
       </c>
       <c r="N210" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B210, $C$2:$C$695, C210, $D$2:$D$695, D210, $E$2:$E$695, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O210" s="38" t="s">
@@ -31549,7 +31548,7 @@
         <v>118</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B211, $C$2:$C$695, C211, $D$2:$D$695, D211, $E$2:$E$695, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31585,7 +31584,7 @@
         <v>55</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B212, $C$2:$C$695, C212, $D$2:$D$695, D212, $E$2:$E$695, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31631,7 +31630,7 @@
         <v>650</v>
       </c>
       <c r="N213" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B213, $C$2:$C$695, C213, $D$2:$D$695, D213, $E$2:$E$695, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P213" s="29"/>
@@ -31678,7 +31677,7 @@
         <v>260</v>
       </c>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B214, $C$2:$C$695, C214, $D$2:$D$695, D214, $E$2:$E$695, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31724,7 +31723,7 @@
         <v>650</v>
       </c>
       <c r="N215" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B215, $C$2:$C$695, C215, $D$2:$D$695, D215, $E$2:$E$695, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O215"/>
@@ -31772,7 +31771,7 @@
         <v>360</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B216, $C$2:$C$695, C216, $D$2:$D$695, D216, $E$2:$E$695, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31806,7 +31805,7 @@
       </c>
       <c r="J217" s="34"/>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B217, $C$2:$C$695, C217, $D$2:$D$695, D217, $E$2:$E$695, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31852,7 +31851,7 @@
         <v>450</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B218, $C$2:$C$695, C218, $D$2:$D$695, D218, $E$2:$E$695, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31898,7 +31897,7 @@
         <v>250</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B219, $C$2:$C$695, C219, $D$2:$D$695, D219, $E$2:$E$695, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P219" s="29"/>
@@ -31935,7 +31934,7 @@
         <v>118</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B220, $C$2:$C$695, C220, $D$2:$D$695, D220, $E$2:$E$695, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31981,7 +31980,7 @@
         <v>320</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B221, $C$2:$C$695, C221, $D$2:$D$695, D221, $E$2:$E$695, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32027,7 +32026,7 @@
         <v>448</v>
       </c>
       <c r="N222" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B222, $C$2:$C$695, C222, $D$2:$D$695, D222, $E$2:$E$695, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32073,7 +32072,7 @@
         <v>651</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B223, $C$2:$C$695, C223, $D$2:$D$695, D223, $E$2:$E$695, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32107,7 +32106,7 @@
       </c>
       <c r="J224" s="34"/>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B224, $C$2:$C$695, C224, $D$2:$D$695, D224, $E$2:$E$695, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32153,7 +32152,7 @@
         <v>47480</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B225, $C$2:$C$695, C225, $D$2:$D$695, D225, $E$2:$E$695, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32187,7 +32186,7 @@
       </c>
       <c r="J226" s="34"/>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B226, $C$2:$C$695, C226, $D$2:$D$695, D226, $E$2:$E$695, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32233,7 +32232,7 @@
         <v>340</v>
       </c>
       <c r="N227" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B227, $C$2:$C$695, C227, $D$2:$D$695, D227, $E$2:$E$695, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32269,7 +32268,7 @@
         <v>118</v>
       </c>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B228, $C$2:$C$695, C228, $D$2:$D$695, D228, $E$2:$E$695, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32305,7 +32304,7 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B229, $C$2:$C$695, C229, $D$2:$D$695, D229, $E$2:$E$695, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32341,7 +32340,7 @@
         <v>118</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B230, $C$2:$C$695, C230, $D$2:$D$695, D230, $E$2:$E$695, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="29"/>
@@ -32376,7 +32375,7 @@
       </c>
       <c r="J231" s="34"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B231, $C$2:$C$695, C231, $D$2:$D$695, D231, $E$2:$E$695, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32415,7 +32414,7 @@
         <v>146</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B232, $C$2:$C$695, C232, $D$2:$D$695, D232, $E$2:$E$695, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32461,7 +32460,7 @@
         <v>300</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B233, $C$2:$C$695, C233, $D$2:$D$695, D233, $E$2:$E$695, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O233" s="10"/>
@@ -32500,7 +32499,7 @@
       <c r="L234" s="18"/>
       <c r="M234" s="18"/>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B234, $C$2:$C$695, C234, $D$2:$D$695, D234, $E$2:$E$695, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O234" s="10"/>
@@ -32536,7 +32535,7 @@
       </c>
       <c r="J235" s="34"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B235, $C$2:$C$695, C235, $D$2:$D$695, D235, $E$2:$E$695, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32572,7 +32571,7 @@
         <v>117</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B236, $C$2:$C$695, C236, $D$2:$D$695, D236, $E$2:$E$695, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P236" s="29"/>
@@ -32607,7 +32606,7 @@
       </c>
       <c r="J237" s="34"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B237, $C$2:$C$695, C237, $D$2:$D$695, D237, $E$2:$E$695, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32643,7 +32642,7 @@
         <v>117</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B238, $C$2:$C$695, C238, $D$2:$D$695, D238, $E$2:$E$695, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32677,7 +32676,7 @@
       </c>
       <c r="J239" s="34"/>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B239, $C$2:$C$695, C239, $D$2:$D$695, D239, $E$2:$E$695, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32723,7 +32722,7 @@
         <v>300</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B240, $C$2:$C$695, C240, $D$2:$D$695, D240, $E$2:$E$695, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32769,7 +32768,7 @@
         <v>300</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B241, $C$2:$C$695, C241, $D$2:$D$695, D241, $E$2:$E$695, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32815,7 +32814,7 @@
         <v>400</v>
       </c>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B242, $C$2:$C$695, C242, $D$2:$D$695, D242, $E$2:$E$695, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32851,7 +32850,7 @@
         <v>117</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B243, $C$2:$C$695, C243, $D$2:$D$695, D243, $E$2:$E$695, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32892,7 +32891,7 @@
       <c r="L244" s="17"/>
       <c r="M244" s="17"/>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B244, $C$2:$C$695, C244, $D$2:$D$695, D244, $E$2:$E$695, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32938,7 +32937,7 @@
         <v>1800</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B245, $C$2:$C$695, C245, $D$2:$D$695, D245, $E$2:$E$695, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32984,7 +32983,7 @@
         <v>268</v>
       </c>
       <c r="N246" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B246, $C$2:$C$695, C246, $D$2:$D$695, D246, $E$2:$E$695, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O246" s="10"/>
@@ -33020,7 +33019,7 @@
       </c>
       <c r="J247" s="34"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B247, $C$2:$C$695, C247, $D$2:$D$695, D247, $E$2:$E$695, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33056,7 +33055,7 @@
         <v>118</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B248, $C$2:$C$695, C248, $D$2:$D$695, D248, $E$2:$E$695, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33102,7 +33101,7 @@
         <v>800</v>
       </c>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B249, $C$2:$C$695, C249, $D$2:$D$695, D249, $E$2:$E$695, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33141,7 +33140,7 @@
       <c r="L250" s="18"/>
       <c r="M250" s="18"/>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B250, $C$2:$C$695, C250, $D$2:$D$695, D250, $E$2:$E$695, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O250" s="10"/>
@@ -33189,7 +33188,7 @@
         <v>260</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B251, $C$2:$C$695, C251, $D$2:$D$695, D251, $E$2:$E$695, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33225,7 +33224,7 @@
         <v>118</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B252, $C$2:$C$695, C252, $D$2:$D$695, D252, $E$2:$E$695, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33271,7 +33270,7 @@
         <v>370</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B253, $C$2:$C$695, C253, $D$2:$D$695, D253, $E$2:$E$695, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="P253" s="29"/>
@@ -33308,7 +33307,7 @@
         <v>118</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B254, $C$2:$C$695, C254, $D$2:$D$695, D254, $E$2:$E$695, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33347,7 +33346,7 @@
       <c r="L255" s="18"/>
       <c r="M255" s="18"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B255, $C$2:$C$695, C255, $D$2:$D$695, D255, $E$2:$E$695, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O255" s="10"/>
@@ -33388,7 +33387,7 @@
       <c r="L256" s="18"/>
       <c r="M256" s="18"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B256, $C$2:$C$695, C256, $D$2:$D$695, D256, $E$2:$E$695, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="10"/>
@@ -33426,7 +33425,7 @@
         <v>117</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B257, $C$2:$C$695, C257, $D$2:$D$695, D257, $E$2:$E$695, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="7"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33462,7 +33461,7 @@
         <v>117</v>
       </c>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B258, $C$2:$C$695, C258, $D$2:$D$695, D258, $E$2:$E$695, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N300" si="8">IF(COUNTIFS( $B$2:$B$695, B258, $C$2:$C$695, C258, $D$2:$D$695, D258, $E$2:$E$695, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -33508,7 +33507,7 @@
         <v>650</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B259, $C$2:$C$695, C259, $D$2:$D$695, D259, $E$2:$E$695, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P259" s="10"/>
@@ -33555,7 +33554,7 @@
         <v>250</v>
       </c>
       <c r="N260" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B260, $C$2:$C$695, C260, $D$2:$D$695, D260, $E$2:$E$695, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33601,7 +33600,7 @@
         <v>300</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B261, $C$2:$C$695, C261, $D$2:$D$695, D261, $E$2:$E$695, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33638,7 +33637,7 @@
       <c r="L262" s="18"/>
       <c r="M262" s="18"/>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B262, $C$2:$C$695, C262, $D$2:$D$695, D262, $E$2:$E$695, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P262" s="10"/>
@@ -33685,7 +33684,7 @@
         <v>235</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B263, $C$2:$C$695, C263, $D$2:$D$695, D263, $E$2:$E$695, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="10"/>
@@ -33721,7 +33720,7 @@
       </c>
       <c r="J264" s="34"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B264, $C$2:$C$695, C264, $D$2:$D$695, D264, $E$2:$E$695, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33755,7 +33754,7 @@
       </c>
       <c r="J265" s="34"/>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B265, $C$2:$C$695, C265, $D$2:$D$695, D265, $E$2:$E$695, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="29"/>
@@ -33790,7 +33789,7 @@
       </c>
       <c r="J266" s="34"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B266, $C$2:$C$695, C266, $D$2:$D$695, D266, $E$2:$E$695, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33826,7 +33825,7 @@
         <v>118</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B267, $C$2:$C$695, C267, $D$2:$D$695, D267, $E$2:$E$695, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33872,7 +33871,7 @@
         <v>300</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B268, $C$2:$C$695, C268, $D$2:$D$695, D268, $E$2:$E$695, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33918,7 +33917,7 @@
         <v>285</v>
       </c>
       <c r="N269" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B269, $C$2:$C$695, C269, $D$2:$D$695, D269, $E$2:$E$695, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33964,7 +33963,7 @@
         <v>726</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B270, $C$2:$C$695, C270, $D$2:$D$695, D270, $E$2:$E$695, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34010,7 +34009,7 @@
         <v>500</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B271, $C$2:$C$695, C271, $D$2:$D$695, D271, $E$2:$E$695, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O271" s="38" t="s">
@@ -34049,7 +34048,7 @@
         <v>117</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B272, $C$2:$C$695, C272, $D$2:$D$695, D272, $E$2:$E$695, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34085,7 +34084,7 @@
         <v>118</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B273, $C$2:$C$695, C273, $D$2:$D$695, D273, $E$2:$E$695, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34119,7 +34118,7 @@
       </c>
       <c r="J274" s="34"/>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B274, $C$2:$C$695, C274, $D$2:$D$695, D274, $E$2:$E$695, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P274" s="29"/>
@@ -34154,7 +34153,7 @@
       </c>
       <c r="J275" s="34"/>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B275, $C$2:$C$695, C275, $D$2:$D$695, D275, $E$2:$E$695, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34188,7 +34187,7 @@
       </c>
       <c r="J276" s="34"/>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B276, $C$2:$C$695, C276, $D$2:$D$695, D276, $E$2:$E$695, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34234,7 +34233,7 @@
         <v>275</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B277, $C$2:$C$695, C277, $D$2:$D$695, D277, $E$2:$E$695, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34268,7 +34267,7 @@
       </c>
       <c r="J278" s="34"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B278, $C$2:$C$695, C278, $D$2:$D$695, D278, $E$2:$E$695, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34305,7 +34304,7 @@
       <c r="L279" s="18"/>
       <c r="M279" s="18"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B279, $C$2:$C$695, C279, $D$2:$D$695, D279, $E$2:$E$695, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O279" s="10"/>
@@ -34353,7 +34352,7 @@
         <v>300</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B280, $C$2:$C$695, C280, $D$2:$D$695, D280, $E$2:$E$695, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O280" s="10"/>
@@ -34391,7 +34390,7 @@
         <v>118</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B281, $C$2:$C$695, C281, $D$2:$D$695, D281, $E$2:$E$695, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34437,7 +34436,7 @@
         <v>250</v>
       </c>
       <c r="N282" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B282, $C$2:$C$695, C282, $D$2:$D$695, D282, $E$2:$E$695, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P282" s="29"/>
@@ -34472,7 +34471,7 @@
       </c>
       <c r="J283" s="34"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B283, $C$2:$C$695, C283, $D$2:$D$695, D283, $E$2:$E$695, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="P283" s="29"/>
@@ -34507,7 +34506,7 @@
       </c>
       <c r="J284" s="34"/>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B284, $C$2:$C$695, C284, $D$2:$D$695, D284, $E$2:$E$695, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34543,7 +34542,7 @@
         <v>118</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B285, $C$2:$C$695, C285, $D$2:$D$695, D285, $E$2:$E$695, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34579,7 +34578,7 @@
         <v>118</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B286, $C$2:$C$695, C286, $D$2:$D$695, D286, $E$2:$E$695, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34613,7 +34612,7 @@
       </c>
       <c r="J287" s="34"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B287, $C$2:$C$695, C287, $D$2:$D$695, D287, $E$2:$E$695, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34659,7 +34658,7 @@
         <v>300</v>
       </c>
       <c r="N288" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B288, $C$2:$C$695, C288, $D$2:$D$695, D288, $E$2:$E$695, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34693,7 +34692,7 @@
       </c>
       <c r="J289" s="34"/>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B289, $C$2:$C$695, C289, $D$2:$D$695, D289, $E$2:$E$695, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34727,7 +34726,7 @@
       </c>
       <c r="J290" s="34"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B290, $C$2:$C$695, C290, $D$2:$D$695, D290, $E$2:$E$695, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34763,7 +34762,7 @@
         <v>55</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B291, $C$2:$C$695, C291, $D$2:$D$695, D291, $E$2:$E$695, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34809,7 +34808,7 @@
         <v>250</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B292, $C$2:$C$695, C292, $D$2:$D$695, D292, $E$2:$E$695, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34843,7 +34842,7 @@
       </c>
       <c r="J293" s="34"/>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B293, $C$2:$C$695, C293, $D$2:$D$695, D293, $E$2:$E$695, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34879,7 +34878,7 @@
         <v>118</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B294, $C$2:$C$695, C294, $D$2:$D$695, D294, $E$2:$E$695, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34918,7 +34917,7 @@
       <c r="L295" s="27"/>
       <c r="M295" s="27"/>
       <c r="N295" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B295, $C$2:$C$695, C295, $D$2:$D$695, D295, $E$2:$E$695, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O295" s="29"/>
@@ -34959,7 +34958,7 @@
       <c r="L296" s="27"/>
       <c r="M296" s="27"/>
       <c r="N296" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B296, $C$2:$C$695, C296, $D$2:$D$695, D296, $E$2:$E$695, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
       <c r="O296" s="29"/>
@@ -34997,7 +34996,7 @@
         <v>117</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B297, $C$2:$C$695, C297, $D$2:$D$695, D297, $E$2:$E$695, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35035,7 +35034,7 @@
         <v>376</v>
       </c>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B298, $C$2:$C$695, C298, $D$2:$D$695, D298, $E$2:$E$695, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35069,11 +35068,11 @@
         <v>5450</v>
       </c>
       <c r="M299" s="18">
-        <f t="shared" ref="M299:M300" si="4">ABS((D299*E299)-L299)</f>
+        <f t="shared" ref="M299:M300" si="9">ABS((D299*E299)-L299)</f>
         <v>295</v>
       </c>
       <c r="N299" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B299, $C$2:$C$695, C299, $D$2:$D$695, D299, $E$2:$E$695, E299) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
@@ -35107,11 +35106,11 @@
         <v>3180</v>
       </c>
       <c r="M300" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>300</v>
       </c>
       <c r="N300" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$695, B300, $C$2:$C$695, C300, $D$2:$D$695, D300, $E$2:$E$695, E300) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="8"/>
         <v>Unique</v>
       </c>
     </row>
